--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janak\Desktop\chip_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE8E19AA-311D-4766-ACDF-D936D1794E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7CCBF4-9CCD-4AB1-9F8C-09A2106676B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E01B0AB-BD68-4F76-B5AA-846182E56997}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="373">
   <si>
     <t>22AD121500004000</t>
   </si>
@@ -1007,6 +1007,141 @@
   </si>
   <si>
     <t>8658061600004000</t>
+  </si>
+  <si>
+    <t>47AF121500004000</t>
+  </si>
+  <si>
+    <t>6258061600004000</t>
+  </si>
+  <si>
+    <t>735A061600004000</t>
+  </si>
+  <si>
+    <t>15AD121500004000</t>
+  </si>
+  <si>
+    <t>D1AC121500004000</t>
+  </si>
+  <si>
+    <t>A9AC121500004000</t>
+  </si>
+  <si>
+    <t>49AF121500004000</t>
+  </si>
+  <si>
+    <t>45BA051600004000</t>
+  </si>
+  <si>
+    <t>805A061600004000</t>
+  </si>
+  <si>
+    <t>64090A1600004000</t>
+  </si>
+  <si>
+    <t>86090A1600004000</t>
+  </si>
+  <si>
+    <t>B53A061600004000</t>
+  </si>
+  <si>
+    <t>C43A061600004000</t>
+  </si>
+  <si>
+    <t>AF3A061600004000</t>
+  </si>
+  <si>
+    <t>2C3B061600004000</t>
+  </si>
+  <si>
+    <t>A93A061600004000</t>
+  </si>
+  <si>
+    <t>C758061600004000</t>
+  </si>
+  <si>
+    <t>9158061600004000</t>
+  </si>
+  <si>
+    <t>84BA051600004000</t>
+  </si>
+  <si>
+    <t>89BA051600004000</t>
+  </si>
+  <si>
+    <t>053B061600004000</t>
+  </si>
+  <si>
+    <t>2E3B061600004000</t>
+  </si>
+  <si>
+    <t>C13A061600004000</t>
+  </si>
+  <si>
+    <t>53BD1C1600004000</t>
+  </si>
+  <si>
+    <t>BEBA051600004000</t>
+  </si>
+  <si>
+    <t>F03A061600004000</t>
+  </si>
+  <si>
+    <t>3B3B061600004000</t>
+  </si>
+  <si>
+    <t>A0AC121500004000</t>
+  </si>
+  <si>
+    <t>12AD121500004000</t>
+  </si>
+  <si>
+    <t>EB58061600004000</t>
+  </si>
+  <si>
+    <t>A9BA051600004000</t>
+  </si>
+  <si>
+    <t>523B061600004000</t>
+  </si>
+  <si>
+    <t>785A061600004000</t>
+  </si>
+  <si>
+    <t>E43A061600004000</t>
+  </si>
+  <si>
+    <t>A13A061600004000</t>
+  </si>
+  <si>
+    <t>433B061600004000</t>
+  </si>
+  <si>
+    <t>CD58061600004000</t>
+  </si>
+  <si>
+    <t>6CB61C1600004000</t>
+  </si>
+  <si>
+    <t>12BA051600004000</t>
+  </si>
+  <si>
+    <t>F859061600004000</t>
+  </si>
+  <si>
+    <t>423B061600004000</t>
+  </si>
+  <si>
+    <t>9F3A061600004000</t>
+  </si>
+  <si>
+    <t>CEBA051600004000</t>
+  </si>
+  <si>
+    <t>865A061600004000</t>
+  </si>
+  <si>
+    <t>EF0A0A1600004000</t>
   </si>
 </sst>
 </file>
@@ -1606,8 +1741,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C528" totalsRowShown="0">
-  <autoFilter ref="A1:C528" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C999" totalsRowShown="0">
+  <autoFilter ref="A1:C999" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C528">
     <sortCondition ref="C1:C528"/>
   </sortState>
@@ -1937,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85308AED-E7F4-43C8-AFEE-DDE995A3E6EF}">
-  <dimension ref="A1:L528"/>
+  <dimension ref="A1:C999"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -7753,6 +7888,5187 @@
         <v>77</v>
       </c>
     </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" s="2">
+        <v>46057.27847222222</v>
+      </c>
+      <c r="B529" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" s="2">
+        <v>46057.27847222222</v>
+      </c>
+      <c r="B530" s="7">
+        <v>10</v>
+      </c>
+      <c r="C530" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" s="2">
+        <v>46057.27847222222</v>
+      </c>
+      <c r="B531" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" s="2">
+        <v>46057.279166666667</v>
+      </c>
+      <c r="B532" s="7">
+        <v>20</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" s="2">
+        <v>46057.279861111114</v>
+      </c>
+      <c r="B533" s="7">
+        <v>10</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" s="2">
+        <v>46057.280555555553</v>
+      </c>
+      <c r="B534" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C534" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" s="2">
+        <v>46057.280555555553</v>
+      </c>
+      <c r="B535" s="7">
+        <v>38.5</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" s="2">
+        <v>46057.28125</v>
+      </c>
+      <c r="B536" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C536" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" s="2">
+        <v>46057.28125</v>
+      </c>
+      <c r="B537" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" s="2">
+        <v>46057.28125</v>
+      </c>
+      <c r="B538" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" s="2">
+        <v>46057.281944444447</v>
+      </c>
+      <c r="B539" s="7">
+        <v>5</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" s="2">
+        <v>46057.282638888886</v>
+      </c>
+      <c r="B540" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" s="2">
+        <v>46057.282638888886</v>
+      </c>
+      <c r="B541" s="7">
+        <v>33</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" s="2">
+        <v>46057.283333333333</v>
+      </c>
+      <c r="B542" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" s="2">
+        <v>46057.28402777778</v>
+      </c>
+      <c r="B543" s="7">
+        <v>7</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" s="2">
+        <v>46057.28402777778</v>
+      </c>
+      <c r="B544" s="7">
+        <v>14</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" s="2">
+        <v>46057.28402777778</v>
+      </c>
+      <c r="B545" s="7">
+        <v>47</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" s="2">
+        <v>46057.284722222219</v>
+      </c>
+      <c r="B546" s="7">
+        <v>11</v>
+      </c>
+      <c r="C546" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" s="2">
+        <v>46057.285416666666</v>
+      </c>
+      <c r="B547" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" s="2">
+        <v>46057.285416666666</v>
+      </c>
+      <c r="B548" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" s="2">
+        <v>46057.285416666666</v>
+      </c>
+      <c r="B549" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" s="2">
+        <v>46057.286111111112</v>
+      </c>
+      <c r="B550" s="7">
+        <v>8</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" s="2">
+        <v>46057.286111111112</v>
+      </c>
+      <c r="B551" s="7">
+        <v>24</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" s="2">
+        <v>46057.286111111112</v>
+      </c>
+      <c r="B552" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" s="2">
+        <v>46057.286805555559</v>
+      </c>
+      <c r="B553" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" s="2">
+        <v>46057.287499999999</v>
+      </c>
+      <c r="B554" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" s="2">
+        <v>46057.287499999999</v>
+      </c>
+      <c r="B555" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" s="2">
+        <v>46057.288194444445</v>
+      </c>
+      <c r="B556" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" s="2">
+        <v>46057.288194444445</v>
+      </c>
+      <c r="B557" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" s="2">
+        <v>46057.288194444445</v>
+      </c>
+      <c r="B558" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" s="2">
+        <v>46057.288888888892</v>
+      </c>
+      <c r="B559" s="7">
+        <v>10</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" s="2">
+        <v>46057.288888888892</v>
+      </c>
+      <c r="B560" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C560" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" s="2">
+        <v>46057.289583333331</v>
+      </c>
+      <c r="B561" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" s="2">
+        <v>46057.289583333331</v>
+      </c>
+      <c r="B562" s="7">
+        <v>51</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" s="2">
+        <v>46057.290277777778</v>
+      </c>
+      <c r="B563" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" s="2">
+        <v>46057.290972222225</v>
+      </c>
+      <c r="B564" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" s="2">
+        <v>46057.290972222225</v>
+      </c>
+      <c r="B565" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" s="2">
+        <v>46057.291666666664</v>
+      </c>
+      <c r="B566" s="7">
+        <v>7</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" s="2">
+        <v>46057.292361111111</v>
+      </c>
+      <c r="B567" s="7">
+        <v>37</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" s="2">
+        <v>46057.292361111111</v>
+      </c>
+      <c r="B568" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" s="2">
+        <v>46057.293055555558</v>
+      </c>
+      <c r="B569" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" s="2">
+        <v>46057.293749999997</v>
+      </c>
+      <c r="B570" s="7">
+        <v>8</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" s="2">
+        <v>46057.293749999997</v>
+      </c>
+      <c r="B571" s="7">
+        <v>23</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" s="2">
+        <v>46057.29583333333</v>
+      </c>
+      <c r="B572" s="7">
+        <v>65</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" s="2">
+        <v>46057.297222222223</v>
+      </c>
+      <c r="B573" s="7">
+        <v>18</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" s="2">
+        <v>46057.29791666667</v>
+      </c>
+      <c r="B574" s="7">
+        <v>8</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" s="2">
+        <v>46057.298611111109</v>
+      </c>
+      <c r="B575" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" s="2">
+        <v>46057.301388888889</v>
+      </c>
+      <c r="B576" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" s="2">
+        <v>46057.302083333336</v>
+      </c>
+      <c r="B577" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" s="2">
+        <v>46057.302083333336</v>
+      </c>
+      <c r="B578" s="7">
+        <v>17</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" s="2">
+        <v>46057.302777777775</v>
+      </c>
+      <c r="B579" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" s="2">
+        <v>46057.302777777775</v>
+      </c>
+      <c r="B580" s="7">
+        <v>32</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" s="2">
+        <v>46057.302777777775</v>
+      </c>
+      <c r="B581" s="7">
+        <v>11</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" s="2">
+        <v>46057.302777777775</v>
+      </c>
+      <c r="B582" s="7">
+        <v>22</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" s="2">
+        <v>46057.303472222222</v>
+      </c>
+      <c r="B583" s="7">
+        <v>9</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" s="2">
+        <v>46057.303472222222</v>
+      </c>
+      <c r="B584" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" s="2">
+        <v>46057.303472222222</v>
+      </c>
+      <c r="B585" s="7">
+        <v>9</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" s="2">
+        <v>46057.304166666669</v>
+      </c>
+      <c r="B586" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A587" s="2">
+        <v>46057.304166666669</v>
+      </c>
+      <c r="B587" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A588" s="2">
+        <v>46057.304861111108</v>
+      </c>
+      <c r="B588" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A589" s="2">
+        <v>46057.304861111108</v>
+      </c>
+      <c r="B589" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A590" s="2">
+        <v>46057.304861111108</v>
+      </c>
+      <c r="B590" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" s="2">
+        <v>46057.305555555555</v>
+      </c>
+      <c r="B591" s="7">
+        <v>6</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A592" s="2">
+        <v>46057.305555555555</v>
+      </c>
+      <c r="B592" s="7">
+        <v>0</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A593" s="2">
+        <v>46057.306250000001</v>
+      </c>
+      <c r="B593" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A594" s="2">
+        <v>46057.306250000001</v>
+      </c>
+      <c r="B594" s="7">
+        <v>13</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A595" s="2">
+        <v>46057.306944444441</v>
+      </c>
+      <c r="B595" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A596" s="2">
+        <v>46057.307638888888</v>
+      </c>
+      <c r="B596" s="7">
+        <v>8</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A597" s="2">
+        <v>46057.308333333334</v>
+      </c>
+      <c r="B597" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A598" s="2">
+        <v>46057.311111111114</v>
+      </c>
+      <c r="B598" s="7">
+        <v>7</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A599" s="2">
+        <v>46057.311111111114</v>
+      </c>
+      <c r="B599" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A600" s="2">
+        <v>46057.311111111114</v>
+      </c>
+      <c r="B600" s="7">
+        <v>13</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A601" s="2">
+        <v>46057.311805555553</v>
+      </c>
+      <c r="B601" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C601" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A602" s="2">
+        <v>46057.3125</v>
+      </c>
+      <c r="B602" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A603" s="2">
+        <v>46057.3125</v>
+      </c>
+      <c r="B603" s="7">
+        <v>36.5</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A604" s="2">
+        <v>46057.3125</v>
+      </c>
+      <c r="B604" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A605" s="2">
+        <v>46057.313194444447</v>
+      </c>
+      <c r="B605" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A606" s="2">
+        <v>46057.313194444447</v>
+      </c>
+      <c r="B606" s="7">
+        <v>11</v>
+      </c>
+      <c r="C606" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A607" s="2">
+        <v>46057.31527777778</v>
+      </c>
+      <c r="B607" s="7">
+        <v>7</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A608" s="2">
+        <v>46057.31527777778</v>
+      </c>
+      <c r="B608" s="7">
+        <v>12</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A609" s="2">
+        <v>46057.315972222219</v>
+      </c>
+      <c r="B609" s="7">
+        <v>10</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A610" s="2">
+        <v>46057.315972222219</v>
+      </c>
+      <c r="B610" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A611" s="2">
+        <v>46057.316666666666</v>
+      </c>
+      <c r="B611" s="7">
+        <v>14</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A612" s="2">
+        <v>46057.317361111112</v>
+      </c>
+      <c r="B612" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A613" s="2">
+        <v>46057.318055555559</v>
+      </c>
+      <c r="B613" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A614" s="2">
+        <v>46057.320833333331</v>
+      </c>
+      <c r="B614" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A615" s="2">
+        <v>46057.322222222225</v>
+      </c>
+      <c r="B615" s="7">
+        <v>17</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A616" s="2">
+        <v>46057.322222222225</v>
+      </c>
+      <c r="B616" s="7">
+        <v>11</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A617" s="2">
+        <v>46057.322222222225</v>
+      </c>
+      <c r="B617" s="7">
+        <v>21</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A618" s="2">
+        <v>46057.322222222225</v>
+      </c>
+      <c r="B618" s="7">
+        <v>14</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A619" s="2">
+        <v>46057.322222222225</v>
+      </c>
+      <c r="B619" s="7">
+        <v>15</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A620" s="2">
+        <v>46057.322916666664</v>
+      </c>
+      <c r="B620" s="7">
+        <v>4</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A621" s="2">
+        <v>46057.322916666664</v>
+      </c>
+      <c r="B621" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A622" s="2">
+        <v>46057.322916666664</v>
+      </c>
+      <c r="B622" s="7">
+        <v>15</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A623" s="2">
+        <v>46057.323611111111</v>
+      </c>
+      <c r="B623" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A624" s="2">
+        <v>46057.323611111111</v>
+      </c>
+      <c r="B624" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A625" s="2">
+        <v>46057.323611111111</v>
+      </c>
+      <c r="B625" s="7">
+        <v>14</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A626" s="2">
+        <v>46057.323611111111</v>
+      </c>
+      <c r="B626" s="7">
+        <v>9</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A627" s="2">
+        <v>46057.323611111111</v>
+      </c>
+      <c r="B627" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A628" s="2">
+        <v>46057.324305555558</v>
+      </c>
+      <c r="B628" s="7">
+        <v>15</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A629" s="2">
+        <v>46057.325694444444</v>
+      </c>
+      <c r="B629" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A630" s="2">
+        <v>46057.325694444444</v>
+      </c>
+      <c r="B630" s="7">
+        <v>10</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A631" s="2">
+        <v>46057.326388888891</v>
+      </c>
+      <c r="B631" s="7">
+        <v>12</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A632" s="2">
+        <v>46057.326388888891</v>
+      </c>
+      <c r="B632" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A633" s="2">
+        <v>46057.32708333333</v>
+      </c>
+      <c r="B633" s="7">
+        <v>8</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A634" s="2">
+        <v>46057.329861111109</v>
+      </c>
+      <c r="B634" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A635" s="2">
+        <v>46057.329861111109</v>
+      </c>
+      <c r="B635" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A636" s="2">
+        <v>46057.330555555556</v>
+      </c>
+      <c r="B636" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A637" s="2">
+        <v>46057.330555555556</v>
+      </c>
+      <c r="B637" s="7">
+        <v>26</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A638" s="2">
+        <v>46057.331250000003</v>
+      </c>
+      <c r="B638" s="7">
+        <v>25</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A639" s="2">
+        <v>46057.331944444442</v>
+      </c>
+      <c r="B639" s="7">
+        <v>18</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A640" s="2">
+        <v>46057.332638888889</v>
+      </c>
+      <c r="B640" s="7">
+        <v>7</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A641" s="2">
+        <v>46057.332638888889</v>
+      </c>
+      <c r="B641" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A642" s="2">
+        <v>46057.333333333336</v>
+      </c>
+      <c r="B642" s="7">
+        <v>18</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A643" s="2">
+        <v>46057.333333333336</v>
+      </c>
+      <c r="B643" s="7">
+        <v>2</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A644" s="2">
+        <v>46057.334027777775</v>
+      </c>
+      <c r="B644" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A645" s="2">
+        <v>46057.335416666669</v>
+      </c>
+      <c r="B645" s="7">
+        <v>16</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A646" s="2">
+        <v>46057.336111111108</v>
+      </c>
+      <c r="B646" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A647" s="2">
+        <v>46057.336805555555</v>
+      </c>
+      <c r="B647" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A648" s="2">
+        <v>46057.337500000001</v>
+      </c>
+      <c r="B648" s="7">
+        <v>80</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A649" s="2">
+        <v>46057.338194444441</v>
+      </c>
+      <c r="B649" s="7">
+        <v>25</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A650" s="2">
+        <v>46057.338888888888</v>
+      </c>
+      <c r="B650" s="7">
+        <v>23</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A651" s="2">
+        <v>46057.339583333334</v>
+      </c>
+      <c r="B651" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A652" s="2">
+        <v>46057.340277777781</v>
+      </c>
+      <c r="B652" s="7">
+        <v>16</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A653" s="2">
+        <v>46057.340277777781</v>
+      </c>
+      <c r="B653" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A654" s="2">
+        <v>46057.342361111114</v>
+      </c>
+      <c r="B654" s="7">
+        <v>65</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A655" s="2">
+        <v>46057.342361111114</v>
+      </c>
+      <c r="B655" s="7">
+        <v>15</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A656" s="2">
+        <v>46057.345833333333</v>
+      </c>
+      <c r="B656" s="7">
+        <v>100</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A657" s="2">
+        <v>46057.34652777778</v>
+      </c>
+      <c r="B657" s="7">
+        <v>6</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A658" s="2">
+        <v>46057.347916666666</v>
+      </c>
+      <c r="B658" s="7">
+        <v>85</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A659" s="2">
+        <v>46057.348611111112</v>
+      </c>
+      <c r="B659" s="7">
+        <v>175</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A660" s="2">
+        <v>46057.349305555559</v>
+      </c>
+      <c r="B660" s="7">
+        <v>15</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A661" s="2">
+        <v>46057.349305555559</v>
+      </c>
+      <c r="B661" s="7">
+        <v>35</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A662" s="2">
+        <v>46057.349305555559</v>
+      </c>
+      <c r="B662" s="7">
+        <v>12</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A663" s="2">
+        <v>46057.35</v>
+      </c>
+      <c r="B663" s="7">
+        <v>15</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A664" s="2">
+        <v>46057.35</v>
+      </c>
+      <c r="B664" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A665" s="2">
+        <v>46057.35</v>
+      </c>
+      <c r="B665" s="7">
+        <v>14</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A666" s="2">
+        <v>46057.350694444445</v>
+      </c>
+      <c r="B666" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A667" s="2">
+        <v>46057.350694444445</v>
+      </c>
+      <c r="B667" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A668" s="2">
+        <v>46057.351388888892</v>
+      </c>
+      <c r="B668" s="7">
+        <v>7</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A669" s="2">
+        <v>46057.351388888892</v>
+      </c>
+      <c r="B669" s="7">
+        <v>17</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A670" s="2">
+        <v>46057.351388888892</v>
+      </c>
+      <c r="B670" s="7">
+        <v>8</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A671" s="2">
+        <v>46057.352083333331</v>
+      </c>
+      <c r="B671" s="7">
+        <v>24</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A672" s="2">
+        <v>46057.352083333331</v>
+      </c>
+      <c r="B672" s="7">
+        <v>23</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A673" s="2">
+        <v>46057.352777777778</v>
+      </c>
+      <c r="B673" s="7">
+        <v>22</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A674" s="2">
+        <v>46057.352777777778</v>
+      </c>
+      <c r="B674" s="7">
+        <v>22</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A675" s="2">
+        <v>46057.353472222225</v>
+      </c>
+      <c r="B675" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A676" s="2">
+        <v>46057.354166666664</v>
+      </c>
+      <c r="B676" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A677" s="2">
+        <v>46057.354166666664</v>
+      </c>
+      <c r="B677" s="7">
+        <v>39</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A678" s="2">
+        <v>46057.354861111111</v>
+      </c>
+      <c r="B678" s="7">
+        <v>14</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A679" s="2">
+        <v>46057.379166666666</v>
+      </c>
+      <c r="B679" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A680" s="2">
+        <v>46057.379166666666</v>
+      </c>
+      <c r="B680" s="7">
+        <v>20</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A681" s="2">
+        <v>46057.379861111112</v>
+      </c>
+      <c r="B681" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A682" s="2">
+        <v>46057.379861111112</v>
+      </c>
+      <c r="B682" s="7">
+        <v>9</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A683" s="2">
+        <v>46057.380555555559</v>
+      </c>
+      <c r="B683" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A684" s="2">
+        <v>46057.381249999999</v>
+      </c>
+      <c r="B684" s="7">
+        <v>9</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A685" s="2">
+        <v>46057.381249999999</v>
+      </c>
+      <c r="B685" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A686" s="2">
+        <v>46057.381944444445</v>
+      </c>
+      <c r="B686" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A687" s="2">
+        <v>46057.381944444445</v>
+      </c>
+      <c r="B687" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A688" s="2">
+        <v>46057.381944444445</v>
+      </c>
+      <c r="B688" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A689" s="2">
+        <v>46057.382638888892</v>
+      </c>
+      <c r="B689" s="7">
+        <v>21</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A690" s="2">
+        <v>46057.384722222225</v>
+      </c>
+      <c r="B690" s="7">
+        <v>17</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A691" s="2">
+        <v>46057.385416666664</v>
+      </c>
+      <c r="B691" s="7">
+        <v>12</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A692" s="2">
+        <v>46057.386805555558</v>
+      </c>
+      <c r="B692" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A693" s="2">
+        <v>46057.386805555558</v>
+      </c>
+      <c r="B693" s="7">
+        <v>9</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A694" s="2">
+        <v>46057.387499999997</v>
+      </c>
+      <c r="B694" s="7">
+        <v>13</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A695" s="2">
+        <v>46057.388194444444</v>
+      </c>
+      <c r="B695" s="7">
+        <v>7</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A696" s="2">
+        <v>46057.388194444444</v>
+      </c>
+      <c r="B696" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A697" s="2">
+        <v>46057.388194444444</v>
+      </c>
+      <c r="B697" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A698" s="2">
+        <v>46057.388194444444</v>
+      </c>
+      <c r="B698" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A699" s="2">
+        <v>46057.38958333333</v>
+      </c>
+      <c r="B699" s="7">
+        <v>23</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A700" s="2">
+        <v>46057.390277777777</v>
+      </c>
+      <c r="B700" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A701" s="2">
+        <v>46057.390277777777</v>
+      </c>
+      <c r="B701" s="7">
+        <v>13</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A702" s="2">
+        <v>46057.390972222223</v>
+      </c>
+      <c r="B702" s="7">
+        <v>11</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A703" s="2">
+        <v>46057.390972222223</v>
+      </c>
+      <c r="B703" s="7">
+        <v>8</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A704" s="2">
+        <v>46057.390972222223</v>
+      </c>
+      <c r="B704" s="7">
+        <v>8</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A705" s="2">
+        <v>46057.392361111109</v>
+      </c>
+      <c r="B705" s="7">
+        <v>30</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A706" s="2">
+        <v>46057.393055555556</v>
+      </c>
+      <c r="B706" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A707" s="2">
+        <v>46057.396527777775</v>
+      </c>
+      <c r="B707" s="7">
+        <v>2</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A708" s="2">
+        <v>46057.396527777775</v>
+      </c>
+      <c r="B708" s="7">
+        <v>13</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A709" s="2">
+        <v>46057.397222222222</v>
+      </c>
+      <c r="B709" s="7">
+        <v>12</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A710" s="2">
+        <v>46057.401388888888</v>
+      </c>
+      <c r="B710" s="7">
+        <v>15</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A711" s="2">
+        <v>46057.401388888888</v>
+      </c>
+      <c r="B711" s="7">
+        <v>13</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A712" s="2">
+        <v>46057.401388888888</v>
+      </c>
+      <c r="B712" s="7">
+        <v>8</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A713" s="2">
+        <v>46057.402083333334</v>
+      </c>
+      <c r="B713" s="7">
+        <v>5</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A714" s="2">
+        <v>46057.402083333334</v>
+      </c>
+      <c r="B714" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A715" s="2">
+        <v>46057.402777777781</v>
+      </c>
+      <c r="B715" s="7">
+        <v>14</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A716" s="2">
+        <v>46057.40347222222</v>
+      </c>
+      <c r="B716" s="7">
+        <v>26</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A717" s="2">
+        <v>46057.40347222222</v>
+      </c>
+      <c r="B717" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A718" s="2">
+        <v>46057.404166666667</v>
+      </c>
+      <c r="B718" s="7">
+        <v>5</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A719" s="2">
+        <v>46057.404166666667</v>
+      </c>
+      <c r="B719" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A720" s="2">
+        <v>46057.404166666667</v>
+      </c>
+      <c r="B720" s="7">
+        <v>8</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A721" s="2">
+        <v>46057.404861111114</v>
+      </c>
+      <c r="B721" s="7">
+        <v>23</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A722" s="2">
+        <v>46057.404861111114</v>
+      </c>
+      <c r="B722" s="7">
+        <v>7</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A723" s="2">
+        <v>46057.405555555553</v>
+      </c>
+      <c r="B723" s="7">
+        <v>16</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A724" s="2">
+        <v>46057.405555555553</v>
+      </c>
+      <c r="B724" s="7">
+        <v>14</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A725" s="2">
+        <v>46057.405555555553</v>
+      </c>
+      <c r="B725" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A726" s="2">
+        <v>46057.40625</v>
+      </c>
+      <c r="B726" s="7">
+        <v>22</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A727" s="2">
+        <v>46057.406944444447</v>
+      </c>
+      <c r="B727" s="7">
+        <v>0</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A728" s="2">
+        <v>46057.407638888886</v>
+      </c>
+      <c r="B728" s="7">
+        <v>32</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A729" s="2">
+        <v>46057.40902777778</v>
+      </c>
+      <c r="B729" s="7">
+        <v>16</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A730" s="2">
+        <v>46057.40902777778</v>
+      </c>
+      <c r="B730" s="7">
+        <v>5</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A731" s="2">
+        <v>46057.40902777778</v>
+      </c>
+      <c r="B731" s="7">
+        <v>12</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A732" s="2">
+        <v>46057.409722222219</v>
+      </c>
+      <c r="B732" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A733" s="2">
+        <v>46057.409722222219</v>
+      </c>
+      <c r="B733" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A734" s="2">
+        <v>46057.413194444445</v>
+      </c>
+      <c r="B734" s="7">
+        <v>9</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A735" s="2">
+        <v>46057.414583333331</v>
+      </c>
+      <c r="B735" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C735" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A736" s="2">
+        <v>46057.414583333331</v>
+      </c>
+      <c r="B736" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A737" s="2">
+        <v>46057.415277777778</v>
+      </c>
+      <c r="B737" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C737" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A738" s="2">
+        <v>46057.415972222225</v>
+      </c>
+      <c r="B738" s="7">
+        <v>5</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A739" s="2">
+        <v>46057.416666666664</v>
+      </c>
+      <c r="B739" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A740" s="2">
+        <v>46057.416666666664</v>
+      </c>
+      <c r="B740" s="7">
+        <v>1</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A741" s="2">
+        <v>46057.416666666664</v>
+      </c>
+      <c r="B741" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A742" s="2">
+        <v>46057.417361111111</v>
+      </c>
+      <c r="B742" s="7">
+        <v>11</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A743" s="2">
+        <v>46057.417361111111</v>
+      </c>
+      <c r="B743" s="7">
+        <v>8</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A744" s="2">
+        <v>46057.418055555558</v>
+      </c>
+      <c r="B744" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A745" s="2">
+        <v>46057.418055555558</v>
+      </c>
+      <c r="B745" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A746" s="2">
+        <v>46057.418055555558</v>
+      </c>
+      <c r="B746" s="7">
+        <v>7</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A747" s="2">
+        <v>46057.418055555558</v>
+      </c>
+      <c r="B747" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A748" s="2">
+        <v>46057.418749999997</v>
+      </c>
+      <c r="B748" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A749" s="2">
+        <v>46057.418749999997</v>
+      </c>
+      <c r="B749" s="7">
+        <v>39</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A750" s="2">
+        <v>46057.419444444444</v>
+      </c>
+      <c r="B750" s="7">
+        <v>6</v>
+      </c>
+      <c r="C750" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A751" s="2">
+        <v>46057.420138888891</v>
+      </c>
+      <c r="B751" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C751" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A752" s="2">
+        <v>46057.420138888891</v>
+      </c>
+      <c r="B752" s="7">
+        <v>11</v>
+      </c>
+      <c r="C752" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A753" s="2">
+        <v>46057.42083333333</v>
+      </c>
+      <c r="B753" s="7">
+        <v>6</v>
+      </c>
+      <c r="C753" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A754" s="2">
+        <v>46057.422222222223</v>
+      </c>
+      <c r="B754" s="7">
+        <v>45</v>
+      </c>
+      <c r="C754" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A755" s="2">
+        <v>46057.424305555556</v>
+      </c>
+      <c r="B755" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C755" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A756" s="2">
+        <v>46057.424305555556</v>
+      </c>
+      <c r="B756" s="7">
+        <v>9</v>
+      </c>
+      <c r="C756" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A757" s="2">
+        <v>46057.425000000003</v>
+      </c>
+      <c r="B757" s="7">
+        <v>22</v>
+      </c>
+      <c r="C757" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A758" s="2">
+        <v>46057.425000000003</v>
+      </c>
+      <c r="B758" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A759" s="2">
+        <v>46057.425694444442</v>
+      </c>
+      <c r="B759" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C759" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A760" s="2">
+        <v>46057.425694444442</v>
+      </c>
+      <c r="B760" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C760" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A761" s="2">
+        <v>46057.426388888889</v>
+      </c>
+      <c r="B761" s="7">
+        <v>6</v>
+      </c>
+      <c r="C761" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A762" s="2">
+        <v>46057.427083333336</v>
+      </c>
+      <c r="B762" s="7">
+        <v>19</v>
+      </c>
+      <c r="C762" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A763" s="2">
+        <v>46057.427083333336</v>
+      </c>
+      <c r="B763" s="7">
+        <v>15</v>
+      </c>
+      <c r="C763" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A764" s="2">
+        <v>46057.427777777775</v>
+      </c>
+      <c r="B764" s="7">
+        <v>5</v>
+      </c>
+      <c r="C764" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A765" s="2">
+        <v>46057.435416666667</v>
+      </c>
+      <c r="B765" s="7">
+        <v>25</v>
+      </c>
+      <c r="C765" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A766" s="2">
+        <v>46057.436111111114</v>
+      </c>
+      <c r="B766" s="7">
+        <v>105</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A767" s="2">
+        <v>46057.436805555553</v>
+      </c>
+      <c r="B767" s="7">
+        <v>150</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A768" s="2">
+        <v>46057.4375</v>
+      </c>
+      <c r="B768" s="7">
+        <v>120</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A769" s="2">
+        <v>46057.438888888886</v>
+      </c>
+      <c r="B769" s="7">
+        <v>125</v>
+      </c>
+      <c r="C769" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A770" s="2">
+        <v>46057.438888888886</v>
+      </c>
+      <c r="B770" s="7">
+        <v>85</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A771" s="2">
+        <v>46057.439583333333</v>
+      </c>
+      <c r="B771" s="7">
+        <v>70</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A772" s="2">
+        <v>46057.44027777778</v>
+      </c>
+      <c r="B772" s="7">
+        <v>75</v>
+      </c>
+      <c r="C772" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A773" s="2">
+        <v>46071.279861111114</v>
+      </c>
+      <c r="B773" s="7">
+        <v>9</v>
+      </c>
+      <c r="C773" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A774" s="2">
+        <v>46071.279861111114</v>
+      </c>
+      <c r="B774" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C774" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A775" s="2">
+        <v>46071.279861111114</v>
+      </c>
+      <c r="B775" s="7">
+        <v>4</v>
+      </c>
+      <c r="C775" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A776" s="2">
+        <v>46071.279861111114</v>
+      </c>
+      <c r="B776" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C776" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A777" s="2">
+        <v>46071.281944444447</v>
+      </c>
+      <c r="B777" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C777" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A778" s="2">
+        <v>46071.282638888886</v>
+      </c>
+      <c r="B778" s="7">
+        <v>9</v>
+      </c>
+      <c r="C778" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A779" s="2">
+        <v>46071.282638888886</v>
+      </c>
+      <c r="B779" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C779" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A780" s="2">
+        <v>46071.283333333333</v>
+      </c>
+      <c r="B780" s="7">
+        <v>12</v>
+      </c>
+      <c r="C780" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A781" s="2">
+        <v>46071.28402777778</v>
+      </c>
+      <c r="B781" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C781" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A782" s="2">
+        <v>46071.284722222219</v>
+      </c>
+      <c r="B782" s="7">
+        <v>14</v>
+      </c>
+      <c r="C782" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A783" s="2">
+        <v>46071.284722222219</v>
+      </c>
+      <c r="B783" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C783" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A784" s="2">
+        <v>46071.285416666666</v>
+      </c>
+      <c r="B784" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C784" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A785" s="2">
+        <v>46071.286111111112</v>
+      </c>
+      <c r="B785" s="7">
+        <v>37</v>
+      </c>
+      <c r="C785" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A786" s="2">
+        <v>46071.286111111112</v>
+      </c>
+      <c r="B786" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C786" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A787" s="2">
+        <v>46071.286805555559</v>
+      </c>
+      <c r="B787" s="7">
+        <v>7</v>
+      </c>
+      <c r="C787" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A788" s="2">
+        <v>46071.286805555559</v>
+      </c>
+      <c r="B788" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C788" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A789" s="2">
+        <v>46071.287499999999</v>
+      </c>
+      <c r="B789" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C789" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A790" s="2">
+        <v>46071.287499999999</v>
+      </c>
+      <c r="B790" s="7">
+        <v>8</v>
+      </c>
+      <c r="C790" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A791" s="2">
+        <v>46071.288194444445</v>
+      </c>
+      <c r="B791" s="7">
+        <v>11</v>
+      </c>
+      <c r="C791" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A792" s="2">
+        <v>46071.288888888892</v>
+      </c>
+      <c r="B792" s="7">
+        <v>7</v>
+      </c>
+      <c r="C792" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A793" s="2">
+        <v>46071.288888888892</v>
+      </c>
+      <c r="B793" s="7">
+        <v>43</v>
+      </c>
+      <c r="C793" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A794" s="2">
+        <v>46071.289583333331</v>
+      </c>
+      <c r="B794" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C794" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A795" s="2">
+        <v>46071.289583333331</v>
+      </c>
+      <c r="B795" s="7">
+        <v>48</v>
+      </c>
+      <c r="C795" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A796" s="2">
+        <v>46071.290277777778</v>
+      </c>
+      <c r="B796" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C796" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A797" s="2">
+        <v>46071.290972222225</v>
+      </c>
+      <c r="B797" s="7">
+        <v>32</v>
+      </c>
+      <c r="C797" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A798" s="2">
+        <v>46071.290972222225</v>
+      </c>
+      <c r="B798" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C798" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A799" s="2">
+        <v>46071.290972222225</v>
+      </c>
+      <c r="B799" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C799" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A800" s="2">
+        <v>46071.291666666664</v>
+      </c>
+      <c r="B800" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C800" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A801" s="2">
+        <v>46071.292361111111</v>
+      </c>
+      <c r="B801" s="7">
+        <v>13</v>
+      </c>
+      <c r="C801" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A802" s="2">
+        <v>46071.293055555558</v>
+      </c>
+      <c r="B802" s="7">
+        <v>8</v>
+      </c>
+      <c r="C802" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A803" s="2">
+        <v>46071.293055555558</v>
+      </c>
+      <c r="B803" s="7">
+        <v>9</v>
+      </c>
+      <c r="C803" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A804" s="2">
+        <v>46071.293055555558</v>
+      </c>
+      <c r="B804" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C804" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A805" s="2">
+        <v>46071.293749999997</v>
+      </c>
+      <c r="B805" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C805" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A806" s="2">
+        <v>46071.294444444444</v>
+      </c>
+      <c r="B806" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C806" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A807" s="2">
+        <v>46071.294444444444</v>
+      </c>
+      <c r="B807" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C807" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A808" s="2">
+        <v>46071.295138888891</v>
+      </c>
+      <c r="B808" s="7">
+        <v>15</v>
+      </c>
+      <c r="C808" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A809" s="2">
+        <v>46071.29583333333</v>
+      </c>
+      <c r="B809" s="7">
+        <v>6</v>
+      </c>
+      <c r="C809" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A810" s="2">
+        <v>46071.296527777777</v>
+      </c>
+      <c r="B810" s="7">
+        <v>9</v>
+      </c>
+      <c r="C810" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A811" s="2">
+        <v>46071.296527777777</v>
+      </c>
+      <c r="B811" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C811" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A812" s="2">
+        <v>46071.297222222223</v>
+      </c>
+      <c r="B812" s="7">
+        <v>39</v>
+      </c>
+      <c r="C812" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A813" s="2">
+        <v>46071.297222222223</v>
+      </c>
+      <c r="B813" s="7">
+        <v>46</v>
+      </c>
+      <c r="C813" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A814" s="2">
+        <v>46071.298611111109</v>
+      </c>
+      <c r="B814" s="7">
+        <v>50</v>
+      </c>
+      <c r="C814" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A815" s="2">
+        <v>46071.3</v>
+      </c>
+      <c r="B815" s="7">
+        <v>12</v>
+      </c>
+      <c r="C815" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A816" s="2">
+        <v>46071.3</v>
+      </c>
+      <c r="B816" s="7">
+        <v>8</v>
+      </c>
+      <c r="C816" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A817" s="2">
+        <v>46071.300694444442</v>
+      </c>
+      <c r="B817" s="7">
+        <v>31</v>
+      </c>
+      <c r="C817" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A818" s="2">
+        <v>46071.301388888889</v>
+      </c>
+      <c r="B818" s="7">
+        <v>17</v>
+      </c>
+      <c r="C818" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A819" s="2">
+        <v>46071.302777777775</v>
+      </c>
+      <c r="B819" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C819" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A820" s="2">
+        <v>46071.302777777775</v>
+      </c>
+      <c r="B820" s="7">
+        <v>15</v>
+      </c>
+      <c r="C820" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A821" s="2">
+        <v>46071.303472222222</v>
+      </c>
+      <c r="B821" s="7">
+        <v>41.5</v>
+      </c>
+      <c r="C821" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A822" s="2">
+        <v>46071.303472222222</v>
+      </c>
+      <c r="B822" s="7">
+        <v>11</v>
+      </c>
+      <c r="C822" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A823" s="2">
+        <v>46071.303472222222</v>
+      </c>
+      <c r="B823" s="7">
+        <v>21</v>
+      </c>
+      <c r="C823" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A824" s="2">
+        <v>46071.304166666669</v>
+      </c>
+      <c r="B824" s="7">
+        <v>13</v>
+      </c>
+      <c r="C824" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A825" s="2">
+        <v>46071.304166666669</v>
+      </c>
+      <c r="B825" s="7">
+        <v>23</v>
+      </c>
+      <c r="C825" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A826" s="2">
+        <v>46071.304861111108</v>
+      </c>
+      <c r="B826" s="7">
+        <v>6</v>
+      </c>
+      <c r="C826" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A827" s="2">
+        <v>46071.304861111108</v>
+      </c>
+      <c r="B827" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C827" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A828" s="2">
+        <v>46071.305555555555</v>
+      </c>
+      <c r="B828" s="7">
+        <v>9</v>
+      </c>
+      <c r="C828" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A829" s="2">
+        <v>46071.306250000001</v>
+      </c>
+      <c r="B829" s="7">
+        <v>8</v>
+      </c>
+      <c r="C829" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A830" s="2">
+        <v>46071.306250000001</v>
+      </c>
+      <c r="B830" s="7">
+        <v>7</v>
+      </c>
+      <c r="C830" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A831" s="2">
+        <v>46071.306250000001</v>
+      </c>
+      <c r="B831" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C831" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A832" s="2">
+        <v>46071.306250000001</v>
+      </c>
+      <c r="B832" s="7">
+        <v>11</v>
+      </c>
+      <c r="C832" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A833" s="2">
+        <v>46071.306944444441</v>
+      </c>
+      <c r="B833" s="7">
+        <v>6</v>
+      </c>
+      <c r="C833" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A834" s="2">
+        <v>46071.306944444441</v>
+      </c>
+      <c r="B834" s="7">
+        <v>3</v>
+      </c>
+      <c r="C834" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A835" s="2">
+        <v>46071.307638888888</v>
+      </c>
+      <c r="B835" s="7">
+        <v>0</v>
+      </c>
+      <c r="C835" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A836" s="2">
+        <v>46071.309027777781</v>
+      </c>
+      <c r="B836" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C836" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A837" s="2">
+        <v>46071.310416666667</v>
+      </c>
+      <c r="B837" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C837" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A838" s="2">
+        <v>46071.311111111114</v>
+      </c>
+      <c r="B838" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C838" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A839" s="2">
+        <v>46071.311111111114</v>
+      </c>
+      <c r="B839" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C839" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A840" s="2">
+        <v>46071.311111111114</v>
+      </c>
+      <c r="B840" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C840" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A841" s="2">
+        <v>46071.311805555553</v>
+      </c>
+      <c r="B841" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C841" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A842" s="2">
+        <v>46071.311805555553</v>
+      </c>
+      <c r="B842" s="7">
+        <v>18</v>
+      </c>
+      <c r="C842" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A843" s="2">
+        <v>46071.3125</v>
+      </c>
+      <c r="B843" s="7">
+        <v>18</v>
+      </c>
+      <c r="C843" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A844" s="2">
+        <v>46071.3125</v>
+      </c>
+      <c r="B844" s="7">
+        <v>10</v>
+      </c>
+      <c r="C844" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A845" s="2">
+        <v>46071.3125</v>
+      </c>
+      <c r="B845" s="7">
+        <v>9</v>
+      </c>
+      <c r="C845" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A846" s="2">
+        <v>46071.3125</v>
+      </c>
+      <c r="B846" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C846" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A847" s="2">
+        <v>46071.3125</v>
+      </c>
+      <c r="B847" s="7">
+        <v>12</v>
+      </c>
+      <c r="C847" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A848" s="2">
+        <v>46071.313194444447</v>
+      </c>
+      <c r="B848" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C848" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A849" s="2">
+        <v>46071.316666666666</v>
+      </c>
+      <c r="B849" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C849" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A850" s="2">
+        <v>46071.316666666666</v>
+      </c>
+      <c r="B850" s="7">
+        <v>7</v>
+      </c>
+      <c r="C850" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A851" s="2">
+        <v>46071.317361111112</v>
+      </c>
+      <c r="B851" s="7">
+        <v>7</v>
+      </c>
+      <c r="C851" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A852" s="2">
+        <v>46071.317361111112</v>
+      </c>
+      <c r="B852" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C852" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A853" s="2">
+        <v>46071.317361111112</v>
+      </c>
+      <c r="B853" s="7">
+        <v>9</v>
+      </c>
+      <c r="C853" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A854" s="2">
+        <v>46071.318055555559</v>
+      </c>
+      <c r="B854" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C854" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A855" s="2">
+        <v>46071.319444444445</v>
+      </c>
+      <c r="B855" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C855" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A856" s="2">
+        <v>46071.320138888892</v>
+      </c>
+      <c r="B856" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C856" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A857" s="2">
+        <v>46071.320138888892</v>
+      </c>
+      <c r="B857" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C857" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A858" s="2">
+        <v>46071.320833333331</v>
+      </c>
+      <c r="B858" s="7">
+        <v>21</v>
+      </c>
+      <c r="C858" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A859" s="2">
+        <v>46071.320833333331</v>
+      </c>
+      <c r="B859" s="7">
+        <v>12</v>
+      </c>
+      <c r="C859" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A860" s="2">
+        <v>46071.321527777778</v>
+      </c>
+      <c r="B860" s="7">
+        <v>19</v>
+      </c>
+      <c r="C860" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A861" s="2">
+        <v>46071.321527777778</v>
+      </c>
+      <c r="B861" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C861" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A862" s="2">
+        <v>46071.321527777778</v>
+      </c>
+      <c r="B862" s="7">
+        <v>45</v>
+      </c>
+      <c r="C862" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A863" s="2">
+        <v>46071.322222222225</v>
+      </c>
+      <c r="B863" s="7">
+        <v>4</v>
+      </c>
+      <c r="C863" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A864" s="2">
+        <v>46071.322916666664</v>
+      </c>
+      <c r="B864" s="7">
+        <v>30</v>
+      </c>
+      <c r="C864" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A865" s="2">
+        <v>46071.32708333333</v>
+      </c>
+      <c r="B865" s="7">
+        <v>16</v>
+      </c>
+      <c r="C865" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A866" s="2">
+        <v>46071.327777777777</v>
+      </c>
+      <c r="B866" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C866" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A867" s="2">
+        <v>46071.327777777777</v>
+      </c>
+      <c r="B867" s="7">
+        <v>20</v>
+      </c>
+      <c r="C867" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A868" s="2">
+        <v>46071.328472222223</v>
+      </c>
+      <c r="B868" s="7">
+        <v>7</v>
+      </c>
+      <c r="C868" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A869" s="2">
+        <v>46071.32916666667</v>
+      </c>
+      <c r="B869" s="7">
+        <v>14</v>
+      </c>
+      <c r="C869" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A870" s="2">
+        <v>46071.331250000003</v>
+      </c>
+      <c r="B870" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C870" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A871" s="2">
+        <v>46071.331944444442</v>
+      </c>
+      <c r="B871" s="7">
+        <v>13</v>
+      </c>
+      <c r="C871" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A872" s="2">
+        <v>46071.332638888889</v>
+      </c>
+      <c r="B872" s="7">
+        <v>30</v>
+      </c>
+      <c r="C872" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A873" s="2">
+        <v>46071.333333333336</v>
+      </c>
+      <c r="B873" s="7">
+        <v>14</v>
+      </c>
+      <c r="C873" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A874" s="2">
+        <v>46071.334027777775</v>
+      </c>
+      <c r="B874" s="7">
+        <v>2</v>
+      </c>
+      <c r="C874" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A875" s="2">
+        <v>46071.334027777775</v>
+      </c>
+      <c r="B875" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C875" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A876" s="2">
+        <v>46071.334027777775</v>
+      </c>
+      <c r="B876" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C876" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A877" s="2">
+        <v>46071.334722222222</v>
+      </c>
+      <c r="B877" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C877" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A878" s="2">
+        <v>46071.335416666669</v>
+      </c>
+      <c r="B878" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C878" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A879" s="2">
+        <v>46071.335416666669</v>
+      </c>
+      <c r="B879" s="7">
+        <v>13</v>
+      </c>
+      <c r="C879" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A880" s="2">
+        <v>46071.336111111108</v>
+      </c>
+      <c r="B880" s="7">
+        <v>12</v>
+      </c>
+      <c r="C880" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A881" s="2">
+        <v>46071.336111111108</v>
+      </c>
+      <c r="B881" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C881" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A882" s="2">
+        <v>46071.336805555555</v>
+      </c>
+      <c r="B882" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C882" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A883" s="2">
+        <v>46071.338194444441</v>
+      </c>
+      <c r="B883" s="7">
+        <v>38</v>
+      </c>
+      <c r="C883" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A884" s="2">
+        <v>46071.338888888888</v>
+      </c>
+      <c r="B884" s="7">
+        <v>9</v>
+      </c>
+      <c r="C884" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A885" s="2">
+        <v>46071.339583333334</v>
+      </c>
+      <c r="B885" s="7">
+        <v>70</v>
+      </c>
+      <c r="C885" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A886" s="2">
+        <v>46071.340277777781</v>
+      </c>
+      <c r="B886" s="7">
+        <v>60</v>
+      </c>
+      <c r="C886" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A887" s="2">
+        <v>46071.34097222222</v>
+      </c>
+      <c r="B887" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C887" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A888" s="2">
+        <v>46071.341666666667</v>
+      </c>
+      <c r="B888" s="7">
+        <v>16</v>
+      </c>
+      <c r="C888" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A889" s="2">
+        <v>46071.343055555553</v>
+      </c>
+      <c r="B889" s="7">
+        <v>30</v>
+      </c>
+      <c r="C889" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A890" s="2">
+        <v>46071.347916666666</v>
+      </c>
+      <c r="B890" s="7">
+        <v>20</v>
+      </c>
+      <c r="C890" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A891" s="2">
+        <v>46071.348611111112</v>
+      </c>
+      <c r="B891" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C891" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A892" s="2">
+        <v>46071.349305555559</v>
+      </c>
+      <c r="B892" s="7">
+        <v>3</v>
+      </c>
+      <c r="C892" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A893" s="2">
+        <v>46071.351388888892</v>
+      </c>
+      <c r="B893" s="7">
+        <v>75</v>
+      </c>
+      <c r="C893" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A894" s="2">
+        <v>46071.352777777778</v>
+      </c>
+      <c r="B894" s="7">
+        <v>235</v>
+      </c>
+      <c r="C894" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A895" s="2">
+        <v>46071.352777777778</v>
+      </c>
+      <c r="B895" s="7">
+        <v>200</v>
+      </c>
+      <c r="C895" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A896" s="2">
+        <v>46071.353472222225</v>
+      </c>
+      <c r="B896" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C896" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A897" s="2">
+        <v>46071.354166666664</v>
+      </c>
+      <c r="B897" s="7">
+        <v>22</v>
+      </c>
+      <c r="C897" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A898" s="2">
+        <v>46071.354166666664</v>
+      </c>
+      <c r="B898" s="7">
+        <v>19</v>
+      </c>
+      <c r="C898" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A899" s="2">
+        <v>46071.354166666664</v>
+      </c>
+      <c r="B899" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C899" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A900" s="2">
+        <v>46071.354861111111</v>
+      </c>
+      <c r="B900" s="7">
+        <v>9</v>
+      </c>
+      <c r="C900" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A901" s="2">
+        <v>46071.354861111111</v>
+      </c>
+      <c r="B901" s="7">
+        <v>9</v>
+      </c>
+      <c r="C901" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A902" s="2">
+        <v>46071.354861111111</v>
+      </c>
+      <c r="B902" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C902" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A903" s="2">
+        <v>46071.355555555558</v>
+      </c>
+      <c r="B903" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C903" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A904" s="2">
+        <v>46071.355555555558</v>
+      </c>
+      <c r="B904" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C904" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A905" s="2">
+        <v>46071.355555555558</v>
+      </c>
+      <c r="B905" s="7">
+        <v>6</v>
+      </c>
+      <c r="C905" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A906" s="2">
+        <v>46071.356249999997</v>
+      </c>
+      <c r="B906" s="7">
+        <v>26</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A907" s="2">
+        <v>46071.356249999997</v>
+      </c>
+      <c r="B907" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A908" s="2">
+        <v>46071.356944444444</v>
+      </c>
+      <c r="B908" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A909" s="2">
+        <v>46071.356944444444</v>
+      </c>
+      <c r="B909" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A910" s="2">
+        <v>46071.357638888891</v>
+      </c>
+      <c r="B910" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A911" s="2">
+        <v>46071.35833333333</v>
+      </c>
+      <c r="B911" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A912" s="2">
+        <v>46071.359027777777</v>
+      </c>
+      <c r="B912" s="7">
+        <v>8</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A913" s="2">
+        <v>46071.359027777777</v>
+      </c>
+      <c r="B913" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A914" s="2">
+        <v>46071.359722222223</v>
+      </c>
+      <c r="B914" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A915" s="2">
+        <v>46071.359722222223</v>
+      </c>
+      <c r="B915" s="7">
+        <v>9</v>
+      </c>
+      <c r="C915" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A916" s="2">
+        <v>46071.36041666667</v>
+      </c>
+      <c r="B916" s="7">
+        <v>24</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A917" s="2">
+        <v>46071.361111111109</v>
+      </c>
+      <c r="B917" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A918" s="2">
+        <v>46071.362500000003</v>
+      </c>
+      <c r="B918" s="7">
+        <v>40</v>
+      </c>
+      <c r="C918" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A919" s="2">
+        <v>46071.363194444442</v>
+      </c>
+      <c r="B919" s="7">
+        <v>50</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A920" s="2">
+        <v>46071.365972222222</v>
+      </c>
+      <c r="B920" s="7">
+        <v>9</v>
+      </c>
+      <c r="C920" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A921" s="2">
+        <v>46071.366666666669</v>
+      </c>
+      <c r="B921" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C921" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A922" s="2">
+        <v>46071.368055555555</v>
+      </c>
+      <c r="B922" s="7">
+        <v>9</v>
+      </c>
+      <c r="C922" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A923" s="2">
+        <v>46071.370138888888</v>
+      </c>
+      <c r="B923" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C923" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A924" s="2">
+        <v>46071.370138888888</v>
+      </c>
+      <c r="B924" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A925" s="2">
+        <v>46071.370833333334</v>
+      </c>
+      <c r="B925" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C925" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A926" s="2">
+        <v>46071.370833333334</v>
+      </c>
+      <c r="B926" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A927" s="2">
+        <v>46071.370833333334</v>
+      </c>
+      <c r="B927" s="7">
+        <v>13</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A928" s="2">
+        <v>46071.371527777781</v>
+      </c>
+      <c r="B928" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A929" s="2">
+        <v>46071.371527777781</v>
+      </c>
+      <c r="B929" s="7">
+        <v>15</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A930" s="2">
+        <v>46071.37222222222</v>
+      </c>
+      <c r="B930" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A931" s="2">
+        <v>46071.37222222222</v>
+      </c>
+      <c r="B931" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A932" s="2">
+        <v>46071.372916666667</v>
+      </c>
+      <c r="B932" s="7">
+        <v>8</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A933" s="2">
+        <v>46071.373611111114</v>
+      </c>
+      <c r="B933" s="7">
+        <v>11</v>
+      </c>
+      <c r="C933" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A934" s="2">
+        <v>46071.374305555553</v>
+      </c>
+      <c r="B934" s="7">
+        <v>12</v>
+      </c>
+      <c r="C934" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A935" s="2">
+        <v>46071.374305555553</v>
+      </c>
+      <c r="B935" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C935" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A936" s="2">
+        <v>46071.374305555553</v>
+      </c>
+      <c r="B936" s="7">
+        <v>14</v>
+      </c>
+      <c r="C936" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A937" s="2">
+        <v>46071.375694444447</v>
+      </c>
+      <c r="B937" s="7">
+        <v>39</v>
+      </c>
+      <c r="C937" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A938" s="2">
+        <v>46071.377083333333</v>
+      </c>
+      <c r="B938" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C938" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A939" s="2">
+        <v>46071.377083333333</v>
+      </c>
+      <c r="B939" s="7">
+        <v>23</v>
+      </c>
+      <c r="C939" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A940" s="2">
+        <v>46071.377083333333</v>
+      </c>
+      <c r="B940" s="7">
+        <v>13</v>
+      </c>
+      <c r="C940" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A941" s="2">
+        <v>46071.377083333333</v>
+      </c>
+      <c r="B941" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C941" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A942" s="2">
+        <v>46071.37777777778</v>
+      </c>
+      <c r="B942" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C942" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A943" s="2">
+        <v>46071.381249999999</v>
+      </c>
+      <c r="B943" s="7">
+        <v>11</v>
+      </c>
+      <c r="C943" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A944" s="2">
+        <v>46071.385416666664</v>
+      </c>
+      <c r="B944" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C944" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A945" s="2">
+        <v>46071.386111111111</v>
+      </c>
+      <c r="B945" s="7">
+        <v>15</v>
+      </c>
+      <c r="C945" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A946" s="2">
+        <v>46071.386805555558</v>
+      </c>
+      <c r="B946" s="7">
+        <v>14</v>
+      </c>
+      <c r="C946" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A947" s="2">
+        <v>46071.387499999997</v>
+      </c>
+      <c r="B947" s="7">
+        <v>14</v>
+      </c>
+      <c r="C947" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A948" s="2">
+        <v>46071.387499999997</v>
+      </c>
+      <c r="B948" s="7">
+        <v>9</v>
+      </c>
+      <c r="C948" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A949" s="2">
+        <v>46071.388194444444</v>
+      </c>
+      <c r="B949" s="7">
+        <v>15</v>
+      </c>
+      <c r="C949" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A950" s="2">
+        <v>46071.388194444444</v>
+      </c>
+      <c r="B950" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C950" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A951" s="2">
+        <v>46071.388888888891</v>
+      </c>
+      <c r="B951" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C951" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A952" s="2">
+        <v>46071.388888888891</v>
+      </c>
+      <c r="B952" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C952" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A953" s="2">
+        <v>46071.38958333333</v>
+      </c>
+      <c r="B953" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C953" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A954" s="2">
+        <v>46071.38958333333</v>
+      </c>
+      <c r="B954" s="7">
+        <v>11</v>
+      </c>
+      <c r="C954" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A955" s="2">
+        <v>46071.38958333333</v>
+      </c>
+      <c r="B955" s="7">
+        <v>10</v>
+      </c>
+      <c r="C955" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A956" s="2">
+        <v>46071.390277777777</v>
+      </c>
+      <c r="B956" s="7">
+        <v>15</v>
+      </c>
+      <c r="C956" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A957" s="2">
+        <v>46071.390972222223</v>
+      </c>
+      <c r="B957" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C957" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A958" s="2">
+        <v>46071.390972222223</v>
+      </c>
+      <c r="B958" s="7">
+        <v>11</v>
+      </c>
+      <c r="C958" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A959" s="2">
+        <v>46071.39166666667</v>
+      </c>
+      <c r="B959" s="7">
+        <v>19</v>
+      </c>
+      <c r="C959" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A960" s="2">
+        <v>46071.39166666667</v>
+      </c>
+      <c r="B960" s="7">
+        <v>7</v>
+      </c>
+      <c r="C960" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A961" s="2">
+        <v>46071.393055555556</v>
+      </c>
+      <c r="B961" s="7">
+        <v>35</v>
+      </c>
+      <c r="C961" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A962" s="2">
+        <v>46071.393750000003</v>
+      </c>
+      <c r="B962" s="7">
+        <v>35</v>
+      </c>
+      <c r="C962" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A963" s="2">
+        <v>46071.394444444442</v>
+      </c>
+      <c r="B963" s="7">
+        <v>15</v>
+      </c>
+      <c r="C963" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A964" s="2">
+        <v>46071.394444444442</v>
+      </c>
+      <c r="B964" s="7">
+        <v>6</v>
+      </c>
+      <c r="C964" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A965" s="2">
+        <v>46071.395138888889</v>
+      </c>
+      <c r="B965" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C965" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A966" s="2">
+        <v>46071.395833333336</v>
+      </c>
+      <c r="B966" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C966" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A967" s="2">
+        <v>46071.395833333336</v>
+      </c>
+      <c r="B967" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C967" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A968" s="2">
+        <v>46071.396527777775</v>
+      </c>
+      <c r="B968" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C968" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A969" s="2">
+        <v>46071.396527777775</v>
+      </c>
+      <c r="B969" s="7">
+        <v>10</v>
+      </c>
+      <c r="C969" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A970" s="2">
+        <v>46071.397222222222</v>
+      </c>
+      <c r="B970" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C970" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A971" s="2">
+        <v>46071.397222222222</v>
+      </c>
+      <c r="B971" s="7">
+        <v>5</v>
+      </c>
+      <c r="C971" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A972" s="2">
+        <v>46071.399305555555</v>
+      </c>
+      <c r="B972" s="7">
+        <v>9</v>
+      </c>
+      <c r="C972" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A973" s="2">
+        <v>46071.399305555555</v>
+      </c>
+      <c r="B973" s="7">
+        <v>33.5</v>
+      </c>
+      <c r="C973" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A974" s="2">
+        <v>46071.4</v>
+      </c>
+      <c r="B974" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C974" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A975" s="2">
+        <v>46071.4</v>
+      </c>
+      <c r="B975" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C975" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A976" s="2">
+        <v>46071.400694444441</v>
+      </c>
+      <c r="B976" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="C976" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A977" s="2">
+        <v>46071.400694444441</v>
+      </c>
+      <c r="B977" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C977" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A978" s="2">
+        <v>46071.401388888888</v>
+      </c>
+      <c r="B978" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C978" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A979" s="2">
+        <v>46071.402083333334</v>
+      </c>
+      <c r="B979" s="7">
+        <v>25</v>
+      </c>
+      <c r="C979" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A980" s="2">
+        <v>46071.402083333334</v>
+      </c>
+      <c r="B980" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C980" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A981" s="2">
+        <v>46071.402083333334</v>
+      </c>
+      <c r="B981" s="7">
+        <v>11</v>
+      </c>
+      <c r="C981" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A982" s="2">
+        <v>46071.402777777781</v>
+      </c>
+      <c r="B982" s="7">
+        <v>24</v>
+      </c>
+      <c r="C982" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A983" s="2">
+        <v>46071.402777777781</v>
+      </c>
+      <c r="B983" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C983" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A984" s="2">
+        <v>46071.402777777781</v>
+      </c>
+      <c r="B984" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C984" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A985" s="2">
+        <v>46071.40347222222</v>
+      </c>
+      <c r="B985" s="7">
+        <v>11</v>
+      </c>
+      <c r="C985" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A986" s="2">
+        <v>46071.404861111114</v>
+      </c>
+      <c r="B986" s="7">
+        <v>20</v>
+      </c>
+      <c r="C986" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A987" s="2">
+        <v>46071.404861111114</v>
+      </c>
+      <c r="B987" s="7">
+        <v>7</v>
+      </c>
+      <c r="C987" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A988" s="2">
+        <v>46071.405555555553</v>
+      </c>
+      <c r="B988" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C988" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A989" s="2">
+        <v>46071.405555555553</v>
+      </c>
+      <c r="B989" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C989" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A990" s="2">
+        <v>46071.40625</v>
+      </c>
+      <c r="B990" s="7">
+        <v>37.5</v>
+      </c>
+      <c r="C990" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A991" s="2">
+        <v>46071.407638888886</v>
+      </c>
+      <c r="B991" s="7">
+        <v>50</v>
+      </c>
+      <c r="C991" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A992" s="2">
+        <v>46071.408333333333</v>
+      </c>
+      <c r="B992" s="7">
+        <v>55</v>
+      </c>
+      <c r="C992" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A993" s="2">
+        <v>46071.40902777778</v>
+      </c>
+      <c r="B993" s="7">
+        <v>70</v>
+      </c>
+      <c r="C993" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A994" s="2">
+        <v>46071.40902777778</v>
+      </c>
+      <c r="B994" s="7">
+        <v>0</v>
+      </c>
+      <c r="C994" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A995" s="2">
+        <v>46071.412499999999</v>
+      </c>
+      <c r="B995" s="7">
+        <v>65</v>
+      </c>
+      <c r="C995" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A996" s="2">
+        <v>46071.413194444445</v>
+      </c>
+      <c r="B996" s="7">
+        <v>95</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A997" s="2">
+        <v>46071.413888888892</v>
+      </c>
+      <c r="B997" s="7">
+        <v>75</v>
+      </c>
+      <c r="C997" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A998" s="2">
+        <v>46071.413888888892</v>
+      </c>
+      <c r="B998" s="7">
+        <v>75</v>
+      </c>
+      <c r="C998" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A999" s="2">
+        <v>46071.424305555556</v>
+      </c>
+      <c r="B999" s="7">
+        <v>2</v>
+      </c>
+      <c r="C999" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janak\Desktop\chip_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7CCBF4-9CCD-4AB1-9F8C-09A2106676B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320A2770-5D02-454D-B94A-2D15E6EF4A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E01B0AB-BD68-4F76-B5AA-846182E56997}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="432">
   <si>
     <t>22AD121500004000</t>
   </si>
@@ -1142,6 +1142,183 @@
   </si>
   <si>
     <t>EF0A0A1600004000</t>
+  </si>
+  <si>
+    <t>60090A1600004000</t>
+  </si>
+  <si>
+    <t>F0AC121500004000</t>
+  </si>
+  <si>
+    <t>17BA051600004000</t>
+  </si>
+  <si>
+    <t>88E8461400004000</t>
+  </si>
+  <si>
+    <t>6BBA051600004000</t>
+  </si>
+  <si>
+    <t>C958061600004000</t>
+  </si>
+  <si>
+    <t>CEAC121500004000</t>
+  </si>
+  <si>
+    <t>F259061600004000</t>
+  </si>
+  <si>
+    <t>A6AC121500004000</t>
+  </si>
+  <si>
+    <t>5558061600004000</t>
+  </si>
+  <si>
+    <t>26E86A1600004000</t>
+  </si>
+  <si>
+    <t>9F1B721600004000</t>
+  </si>
+  <si>
+    <t>CCAC121500004000</t>
+  </si>
+  <si>
+    <t>16AD121500004000</t>
+  </si>
+  <si>
+    <t>0E3B061600004000</t>
+  </si>
+  <si>
+    <t>1E5A061600004000</t>
+  </si>
+  <si>
+    <t>3AAD121500004000</t>
+  </si>
+  <si>
+    <t>CB1B721600004000</t>
+  </si>
+  <si>
+    <t>17C2121500004000</t>
+  </si>
+  <si>
+    <t>1D3B061600004000</t>
+  </si>
+  <si>
+    <t>745A061600004000</t>
+  </si>
+  <si>
+    <t>065A061600004000</t>
+  </si>
+  <si>
+    <t>BF3A061600004000</t>
+  </si>
+  <si>
+    <t>A83A061600004000</t>
+  </si>
+  <si>
+    <t>333B061600004000</t>
+  </si>
+  <si>
+    <t>CA3A061600004000</t>
+  </si>
+  <si>
+    <t>AE3A061600004000</t>
+  </si>
+  <si>
+    <t>FD3A061600004000</t>
+  </si>
+  <si>
+    <t>F10A0A1600004000</t>
+  </si>
+  <si>
+    <t>4F0C0A1600004000</t>
+  </si>
+  <si>
+    <t>1F3B061600004000</t>
+  </si>
+  <si>
+    <t>ED3A061600004000</t>
+  </si>
+  <si>
+    <t>C0BA051600004000</t>
+  </si>
+  <si>
+    <t>5F5A061600004000</t>
+  </si>
+  <si>
+    <t>9BD31C1600004000</t>
+  </si>
+  <si>
+    <t>79BA051600004000</t>
+  </si>
+  <si>
+    <t>BABA051600004000</t>
+  </si>
+  <si>
+    <t>C93A061600004000</t>
+  </si>
+  <si>
+    <t>E13A061600004000</t>
+  </si>
+  <si>
+    <t>E93A061600004000</t>
+  </si>
+  <si>
+    <t>913A061600004000</t>
+  </si>
+  <si>
+    <t>DB3A061600004000</t>
+  </si>
+  <si>
+    <t>6C58061600004000</t>
+  </si>
+  <si>
+    <t>073B061600004000</t>
+  </si>
+  <si>
+    <t>8E3A061600004000</t>
+  </si>
+  <si>
+    <t>413B061600004000</t>
+  </si>
+  <si>
+    <t>74A31C1600004000</t>
+  </si>
+  <si>
+    <t>B93A061600004000</t>
+  </si>
+  <si>
+    <t>1930061600004000</t>
+  </si>
+  <si>
+    <t>A43A061600004000</t>
+  </si>
+  <si>
+    <t>F83A061600004000</t>
+  </si>
+  <si>
+    <t>585A061600004000</t>
+  </si>
+  <si>
+    <t>A63A061600004000</t>
+  </si>
+  <si>
+    <t>383B061600004000</t>
+  </si>
+  <si>
+    <t>9A3A061600004000</t>
+  </si>
+  <si>
+    <t>5D5A061600004000</t>
+  </si>
+  <si>
+    <t>313B061600004000</t>
+  </si>
+  <si>
+    <t>1B3B061600004000</t>
+  </si>
+  <si>
+    <t>FE3A061600004000</t>
   </si>
 </sst>
 </file>
@@ -1741,8 +1918,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C999" totalsRowShown="0">
-  <autoFilter ref="A1:C999" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C1372" totalsRowShown="0">
+  <autoFilter ref="A1:C1372" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C528">
     <sortCondition ref="C1:C528"/>
   </sortState>
@@ -2072,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85308AED-E7F4-43C8-AFEE-DDE995A3E6EF}">
-  <dimension ref="A1:C999"/>
+  <dimension ref="A1:C1372"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -13069,6 +13246,4109 @@
         <v>273</v>
       </c>
     </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1000" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1000" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1001" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1001" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1002" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1002" s="7">
+        <v>35</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1003" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1003" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1004" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1004" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1005" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1005" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1005" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1006" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1006" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1006" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1007" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1007" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1008" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1008" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1009" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1009" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1010" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1010" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1011" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1011" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1012" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1012" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1013" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1013" s="7">
+        <v>48.5</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1014" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1014" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1015" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1015" s="7">
+        <v>37.5</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1016" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1016" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1017" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1017" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1018" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1018" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1019" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1019" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1020" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1020" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1021" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1021" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1022" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1022" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1023" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1023" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1024" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1024" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1025" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1025" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1026" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1026" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1027" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1027" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1028" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1028" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1029" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1029" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1030" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1030" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1031" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1031" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1032" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1032" s="7">
+        <v>27</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1033" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1033" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1034" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1034" s="7">
+        <v>48</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1035" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1035" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1036" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1036" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1037" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1037" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1038" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1038" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1039" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1039" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1040" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1040" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1041" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1041" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1042" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1042" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1043" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1043" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1043" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1044" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1044" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1045" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1045" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1046" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1046" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1047" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1047" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1048" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1048" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1049" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1049" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1050" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1050" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1051" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1051" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1052" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1052" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1053" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1053" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1054" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1054" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1055" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1055" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1056" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1056" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1057" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1057" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1058" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1058" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1059" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1059" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1060" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1060" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1061" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1061" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1062" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1062" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1063" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1063" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1064" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1064" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1065" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1065" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1066" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1066" s="7">
+        <v>42</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1067" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1067" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1068" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1068" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1069" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1069" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1070" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1070" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1071" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1071" s="7">
+        <v>23</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1072" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1072" s="7">
+        <v>55</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1073" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1073" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1074" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1074" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1075" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1075" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1076" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1076" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1077" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1077" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1078" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1078" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1079" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1079" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1080" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1080" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1081" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1081" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1082" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1082" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1083" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1083" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1084" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1084" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1085" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1085" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1086" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1086" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1086" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1087" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1087" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1087" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1088" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1088" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1088" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1089" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1089" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1089" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1090" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1090" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1090" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1091" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1091" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1091" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1092" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1092" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1092" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1093" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1093" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1093" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1094" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1094" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1094" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1095" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1095" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1095" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1096" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1096" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1096" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1097" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1097" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1098" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1098" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1098" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1099" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1099" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1099" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1100" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1100" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1100" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1101" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1101" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1101" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1102" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1102" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1102" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1103" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1103" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1103" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1104" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1104" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1104" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1105" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1105" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1106" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1106" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1107" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1107" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1108" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1108" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1109" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1109" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1110" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1110" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1110" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1111" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1111" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1111" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1112" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1112" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1112" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1113" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1113" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1113" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1114" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1114" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1114" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1115" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1115" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C1115" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1116" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1116" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1116" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1117" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1117" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1117" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1118" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1118" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1118" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1119" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1119" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1119" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1120" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1120" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1120" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1121" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1121" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C1121" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1122" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1122" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1122" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1123" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1123" s="7">
+        <v>24</v>
+      </c>
+      <c r="C1123" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1124" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1124" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1124" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1125" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1125" s="7">
+        <v>23</v>
+      </c>
+      <c r="C1125" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1126" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1126" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1126" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1127" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1127" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1127" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1128" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1128" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1128" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1129" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1129" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1129" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1130" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1130" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1130" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1131" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1131" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1131" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1132" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1132" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1132" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1133" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1133" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1133" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1134" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1134" s="7">
+        <v>65</v>
+      </c>
+      <c r="C1134" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1135" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1135" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C1135" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1136" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1136" s="7">
+        <v>36</v>
+      </c>
+      <c r="C1136" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1137" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1137" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1137" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1138" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1138" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1138" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1139" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1139" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1139" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1140" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1140" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1140" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1141" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1141" s="7">
+        <v>60</v>
+      </c>
+      <c r="C1141" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1142" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1142" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1142" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1143" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1143" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1143" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1144" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1144" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1144" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1145" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1145" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1145" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1146" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1146" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C1146" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1147" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1147" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1147" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1148" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1148" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1148" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1149" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1149" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1149" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1150" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1150" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1150" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1151" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1151" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1151" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1152" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1152" s="7">
+        <v>21</v>
+      </c>
+      <c r="C1152" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1153" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1153" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1153" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1154" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1154" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1154" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1155" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1155" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1155" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1156" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1156" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1156" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1157" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1157" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1157" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1158" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1158" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1158" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1159" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1159" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C1159" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1160" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1160" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1160" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1161" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1161" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1161" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1162" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1162" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1162" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1163" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1163" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1163" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1164" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1164" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1164" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1165" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1165" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1165" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1166" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1166" s="7">
+        <v>47</v>
+      </c>
+      <c r="C1166" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1167" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1167" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C1167" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1168" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1168" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1168" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1169" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1169" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1169" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1170" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1170" s="7">
+        <v>21</v>
+      </c>
+      <c r="C1170" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1171" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1171" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1171" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1172" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1172" s="7">
+        <v>85</v>
+      </c>
+      <c r="C1172" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1173" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1173" s="7">
+        <v>55</v>
+      </c>
+      <c r="C1173" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1174" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1174" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C1174" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1175" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1175" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1175" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1176" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1176" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1176" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1177" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1177" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1177" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1178" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1178" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1178" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1179" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1179" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1179" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1180" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1180" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1180" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1181" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1181" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1181" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1182" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1182" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1182" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1183" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1183" s="7">
+        <v>60</v>
+      </c>
+      <c r="C1183" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1184" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1184" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1184" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1185" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1185" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1185" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1186" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1186" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1186" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1187" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1187" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1187" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1188" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1188" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1188" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1189" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1189" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1189" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1190" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1190" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1190" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1191" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1191" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1191" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1192" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1192" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1192" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1193" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1193" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1193" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1194" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1194" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1194" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1195" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1195" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1195" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1196" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1196" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1196" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1197" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1197" s="7">
+        <v>0</v>
+      </c>
+      <c r="C1197" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1198" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1198" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1198" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1199" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1199" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1199" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1200" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1200" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1200" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1201" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1201" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1201" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1202" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1202" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1202" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1203" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1203" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C1203" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1204" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1204" s="7">
+        <v>70</v>
+      </c>
+      <c r="C1204" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1205" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1205" s="7">
+        <v>240</v>
+      </c>
+      <c r="C1205" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1206" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1206" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1206" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1207" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1207" s="7">
+        <v>29</v>
+      </c>
+      <c r="C1207" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1208" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1208" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1208" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1209" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1209" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1209" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1210" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1210" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1210" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1211" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1211" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1211" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1212" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1212" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1212" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1213" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1213" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1213" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1214" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1214" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1214" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1215" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1215" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1215" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1216" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1216" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1216" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1217" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1217" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1217" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1218" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1218" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C1218" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1219" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1219" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1219" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1220" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1220" s="7">
+        <v>0</v>
+      </c>
+      <c r="C1220" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1221" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1221" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1221" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1222" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1222" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1222" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1223" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1223" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1223" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1224" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1224" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1224" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1225" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1225" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C1225" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1226" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1226" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1226" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1227" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1227" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1227" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1228" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1228" s="7">
+        <v>52</v>
+      </c>
+      <c r="C1228" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1229" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1229" s="7">
+        <v>41</v>
+      </c>
+      <c r="C1229" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1230" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1230" s="7">
+        <v>26</v>
+      </c>
+      <c r="C1230" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1231" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1231" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1231" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1232" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1232" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1232" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1233" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1233" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C1233" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1234" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1234" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C1234" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1235" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1235" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1235" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1236" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1236" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1236" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1237" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1237" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1237" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1238" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1238" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1238" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1239" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1239" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1239" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1240" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1240" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1240" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1241" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1241" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1241" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1242" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1242" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1242" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1243" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1243" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1243" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1244" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1244" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1244" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1245" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1245" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1245" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1246" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1246" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1246" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1247" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1247" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1247" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1248" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1248" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1248" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1249" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1249" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1249" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1250" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1250" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1250" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1251" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1251" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1251" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1252" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1252" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1252" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1253" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1253" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1253" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1254" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1254" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1254" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1255" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1255" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1255" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1256" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1256" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1256" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1257" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1257" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1257" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1258" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1258" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1258" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1259" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1259" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1259" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1260" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1260" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1260" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1261" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1261" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1261" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1262" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1262" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1262" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1263" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1263" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1263" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1264" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1264" s="7">
+        <v>38.5</v>
+      </c>
+      <c r="C1264" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1265" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1265" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1265" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1266" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1266" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1266" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1267" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1267" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1267" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1268" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1268" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1268" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1269" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1269" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1269" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1270" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1270" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1270" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1271" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1271" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1271" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1272" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1272" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1272" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1273" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1273" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1273" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1274" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1274" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1274" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1275" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1275" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1275" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1276" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1276" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1276" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1277" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1277" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1277" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1278" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1278" s="7">
+        <v>0</v>
+      </c>
+      <c r="C1278" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1279" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1279" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1279" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1280" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1280" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1280" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1281" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1281" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1281" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1282" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1282" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1282" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1283" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1283" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1283" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1284" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1284" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1284" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1285" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1285" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1285" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1286" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1286" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1286" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1287" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1287" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1287" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1288" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1288" s="7">
+        <v>0</v>
+      </c>
+      <c r="C1288" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1289" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1289" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1289" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1290" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1290" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1290" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1291" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1291" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1291" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1292" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1292" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1292" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1293" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1293" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1293" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1294" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1294" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1294" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1295" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1295" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1295" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1296" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1296" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1296" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1297" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1297" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1297" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1298" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1298" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1298" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1299" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1299" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1299" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1300" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1300" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1300" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1301" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1301" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1301" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1302" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1302" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1302" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1303" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1303" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1303" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1304" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1304" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1304" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1305" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1305" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1305" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1306" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1306" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1306" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1307" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1307" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1307" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1308" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1308" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1308" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1309" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1309" s="7">
+        <v>24</v>
+      </c>
+      <c r="C1309" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1310" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1310" s="7">
+        <v>39</v>
+      </c>
+      <c r="C1310" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1311" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1311" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1311" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1312" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1312" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1312" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1313" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1313" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1313" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1314" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1314" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1314" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1315" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1315" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1315" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1316" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1316" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1316" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1317" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1317" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1317" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1318" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1318" s="7">
+        <v>50</v>
+      </c>
+      <c r="C1318" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1319" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1319" s="7">
+        <v>55</v>
+      </c>
+      <c r="C1319" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1320" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1320" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1320" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1321" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1321" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1321" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1322" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1322" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1322" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1323" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1323" s="7">
+        <v>23</v>
+      </c>
+      <c r="C1323" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1324" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1324" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1324" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1325" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1325" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1325" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1326" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1326" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1326" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1327" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1327" s="7">
+        <v>30</v>
+      </c>
+      <c r="C1327" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1328" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1328" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1328" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1329" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1329" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1329" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1330" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1330" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1330" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1331" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1331" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1331" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1332" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1332" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1332" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1333" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1333" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1333" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1334" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1334" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1334" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1335" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1335" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1335" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1336" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1336" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1336" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1337" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1337" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1337" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1338" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1338" s="7">
+        <v>115</v>
+      </c>
+      <c r="C1338" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1339" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1339" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1339" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1340" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1340" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1340" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1341" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1341" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1341" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1342" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1342" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1342" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1343" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1343" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1343" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1344" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1344" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C1344" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1345" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1345" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C1345" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1346" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1346" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1346" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1347" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1347" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1347" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1348" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1348" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C1348" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1349" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1349" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1349" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1350" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1350" s="7">
+        <v>26</v>
+      </c>
+      <c r="C1350" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1351" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1351" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C1351" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1352" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1352" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1352" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1353" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1353" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1353" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1354" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1354" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1354" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1355" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1355" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1355" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1356" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1356" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C1356" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1357" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1357" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1357" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1358" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1358" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1358" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1359" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1359" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1359" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1360" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1360" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1360" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1361" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1361" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1361" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1362" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1362" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1362" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1363" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1363" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1363" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1364" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1364" s="7">
+        <v>27</v>
+      </c>
+      <c r="C1364" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1365" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1365" s="7">
+        <v>130</v>
+      </c>
+      <c r="C1365" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1366" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1366" s="7">
+        <v>95</v>
+      </c>
+      <c r="C1366" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1367" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1367" s="7">
+        <v>80</v>
+      </c>
+      <c r="C1367" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1368" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1368" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1368" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1369" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1369" s="7">
+        <v>65</v>
+      </c>
+      <c r="C1369" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1370" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1370" s="7">
+        <v>40</v>
+      </c>
+      <c r="C1370" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1371" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1371" s="7">
+        <v>80</v>
+      </c>
+      <c r="C1371" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1372" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B1372" s="7">
+        <v>95</v>
+      </c>
+      <c r="C1372" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janak\Desktop\chip_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81008EA7-3359-4E6D-B175-1ECA9ABAFC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15EBB495-C26B-46EA-8D9A-C161A28CAAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E01B0AB-BD68-4F76-B5AA-846182E56997}"/>
   </bookViews>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="448">
   <si>
     <t>22AD121500004000</t>
   </si>
@@ -1600,6 +1600,48 @@
   </si>
   <si>
     <t>5458061600004000</t>
+  </si>
+  <si>
+    <t>343B061600004000</t>
+  </si>
+  <si>
+    <t>3CBA051600004000</t>
+  </si>
+  <si>
+    <t>3D1B721600004000</t>
+  </si>
+  <si>
+    <t>475A061600004000</t>
+  </si>
+  <si>
+    <t>50BA051600004000</t>
+  </si>
+  <si>
+    <t>755A061600004000</t>
+  </si>
+  <si>
+    <t>82BA051600004000</t>
+  </si>
+  <si>
+    <t>8C3A061600004000</t>
+  </si>
+  <si>
+    <t>923A061600004000</t>
+  </si>
+  <si>
+    <t>9F1B721600004000</t>
+  </si>
+  <si>
+    <t>A83A061600004000</t>
+  </si>
+  <si>
+    <t>B3AC121500004000</t>
+  </si>
+  <si>
+    <t>C6D0561600004000</t>
+  </si>
+  <si>
+    <t>EC1A721600004000</t>
   </si>
 </sst>
 </file>
@@ -2219,8 +2261,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C1524" totalsRowShown="0">
-  <autoFilter ref="A1:C1524" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C2307" totalsRowShown="0">
+  <autoFilter ref="A1:C2307" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C999">
     <sortCondition ref="A1:A999"/>
   </sortState>
@@ -2550,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85308AED-E7F4-43C8-AFEE-DDE995A3E6EF}">
-  <dimension ref="A1:C1524"/>
+  <dimension ref="A1:C2307"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -19322,8 +19364,8621 @@
         <v>300</v>
       </c>
     </row>
+    <row r="1525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1525" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1525" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1525" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1526" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1526" s="7">
+        <v>47.5</v>
+      </c>
+      <c r="C1526" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1527" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1527" s="7">
+        <v>56</v>
+      </c>
+      <c r="C1527" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1528" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1528" s="7">
+        <v>51</v>
+      </c>
+      <c r="C1528" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1529" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1529" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1529" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1530" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1530" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1530" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1531" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1531" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1531" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1532" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1532" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1532" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1533" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1533" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1533" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1534" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1534" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1534" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1535" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1535" s="7">
+        <v>55</v>
+      </c>
+      <c r="C1535" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1536" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1536" s="7">
+        <v>35</v>
+      </c>
+      <c r="C1536" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1537" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1537" s="7">
+        <v>45</v>
+      </c>
+      <c r="C1537" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1538" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1538" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1538" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1539" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1539" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1539" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1540" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1540" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1540" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1541" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1541" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1541" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1542" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1542" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C1542" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1543" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1543" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1543" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1544" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1544" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1544" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1545" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1545" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1545" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1546" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1546" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1546" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1547" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1547" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1547" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1548" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1548" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1548" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1549" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1549" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1549" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1550" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1550" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1550" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1551" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1551" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1551" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1552" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1552" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1552" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1553" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1553" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1553" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1554" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1554" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C1554" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1555" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1555" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1555" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1556" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1556" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1556" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1557" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1557" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1557" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1558" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1558" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C1558" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1559" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1559" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1559" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1560" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1560" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1560" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1561" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1561" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1561" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1562" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1562" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1562" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1563" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1563" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1563" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1564" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1564" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1564" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1565" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1565" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1565" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1566" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1566" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1566" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1567" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1567" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1567" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1568" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1568" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1568" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1569" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1569" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1569" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1570" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1570" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1570" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1571" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1571" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1571" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1572" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1572" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1572" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1573" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1573" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1573" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1574" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1574" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1574" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1575" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1575" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1575" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1576" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1576" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1576" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1577" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1577" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1577" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1578" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1578" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1578" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1579" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1579" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1579" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1580" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1580" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1580" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1581" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1581" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1581" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1582" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1582" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1582" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1583" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1583" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1583" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1584" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1584" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1584" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1585" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1585" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C1585" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1586" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1586" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1586" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1587" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1587" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C1587" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1588" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1588" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1588" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1589" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1589" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1589" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1590" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1590" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1590" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1591" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1591" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1591" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1592" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1592" s="7">
+        <v>41.5</v>
+      </c>
+      <c r="C1592" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1593" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1593" s="7">
+        <v>35</v>
+      </c>
+      <c r="C1593" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1594" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1594" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1594" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1595" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1595" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1595" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1596" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1596" s="7">
+        <v>105</v>
+      </c>
+      <c r="C1596" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1597" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1597" s="7">
+        <v>50</v>
+      </c>
+      <c r="C1597" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1598" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1598" s="7">
+        <v>55</v>
+      </c>
+      <c r="C1598" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1599" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1599" s="7">
+        <v>65</v>
+      </c>
+      <c r="C1599" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1600" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1600" s="7">
+        <v>40</v>
+      </c>
+      <c r="C1600" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1601" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1601" s="7">
+        <v>50</v>
+      </c>
+      <c r="C1601" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1602" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1602" s="7">
+        <v>110</v>
+      </c>
+      <c r="C1602" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1603" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1603" s="7">
+        <v>105</v>
+      </c>
+      <c r="C1603" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1604" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1604" s="7">
+        <v>135</v>
+      </c>
+      <c r="C1604" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1605" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1605" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1605" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1606" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1606" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1606" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1607" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1607" s="7">
+        <v>42</v>
+      </c>
+      <c r="C1607" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1608" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1608" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1608" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1609" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1609" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1609" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1610" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1610" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1610" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1611" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1611" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1611" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1612" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1612" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1612" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1613" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1613" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1613" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1614" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1614" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1614" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1615" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1615" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1615" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1616" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1616" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1616" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1617" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1617" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1617" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1618" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1618" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1618" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1619" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1619" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1619" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1620" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1620" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1620" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1621" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1621" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1621" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1622" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1622" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1622" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1623" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1623" s="7">
+        <v>105</v>
+      </c>
+      <c r="C1623" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1624" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1624" s="7">
+        <v>65</v>
+      </c>
+      <c r="C1624" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1625" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1625" s="7">
+        <v>90</v>
+      </c>
+      <c r="C1625" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1626" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1626" s="7">
+        <v>30</v>
+      </c>
+      <c r="C1626" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1627" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1627" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1627" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1628" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1628" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1628" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1629" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1629" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1629" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1630" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1630" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1630" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1631" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1631" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1631" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1632" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1632" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1632" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1633" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1633" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1633" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1634" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1634" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1634" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1635" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1635" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1635" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1636" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1636" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1636" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1637" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1637" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1637" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1638" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1638" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1638" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1639" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1639" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1639" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1640" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1640" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C1640" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1641" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1641" s="7">
+        <v>46.5</v>
+      </c>
+      <c r="C1641" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1642" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1642" s="7">
+        <v>30</v>
+      </c>
+      <c r="C1642" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1643" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1643" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1643" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1644" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1644" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1644" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1645" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1645" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1645" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1646" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1646" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1646" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1647" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1647" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1647" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1648" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1648" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1648" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1649" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1649" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1649" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1650" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1650" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C1650" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1651" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1651" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C1651" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1652" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1652" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1652" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1653" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1653" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1653" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1654" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1654" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1654" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1655" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1655" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1655" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1656" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1656" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1656" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1657" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1657" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1657" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1658" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1658" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1658" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1659" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1659" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1659" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1660" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1660" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1660" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1661" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1661" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1661" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1662" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1662" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1662" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1663" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1663" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1663" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1664" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1664" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C1664" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1665" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1665" s="7">
+        <v>49</v>
+      </c>
+      <c r="C1665" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1666" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1666" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1666" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1667" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1667" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1667" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1668" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1668" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1668" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1669" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1669" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1669" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1670" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1670" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1670" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1671" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1671" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1671" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1672" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1672" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1672" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1673" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1673" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1673" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1674" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1674" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1674" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1675" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1675" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1675" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1676" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1676" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1676" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1677" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1677" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1677" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1678" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1678" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1678" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1679" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1679" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1679" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1680" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1680" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1680" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1681" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1681" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1681" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1682" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1682" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1682" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1683" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1683" s="7">
+        <v>21</v>
+      </c>
+      <c r="C1683" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1684" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1684" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1684" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1685" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1685" s="7">
+        <v>31</v>
+      </c>
+      <c r="C1685" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1686" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1686" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C1686" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1687" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1687" s="7">
+        <v>56</v>
+      </c>
+      <c r="C1687" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1688" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1688" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1688" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1689" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1689" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1689" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1690" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1690" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1690" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1691" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1691" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1691" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1692" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1692" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1692" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1693" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1693" s="7">
+        <v>21</v>
+      </c>
+      <c r="C1693" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1694" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1694" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1694" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1695" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1695" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C1695" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1696" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1696" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1696" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1697" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1697" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1697" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1698" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1698" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1698" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1699" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1699" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1699" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1700" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1700" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1700" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1701" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1701" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1701" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1702" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1702" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1702" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1703" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1703" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1703" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1704" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1704" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1704" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1705" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1705" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1705" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1706" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1706" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1706" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1707" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1707" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1707" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1708" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1708" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C1708" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1709" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1709" s="7">
+        <v>30</v>
+      </c>
+      <c r="C1709" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1710" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1710" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1710" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1711" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1711" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1711" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1712" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1712" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1712" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1713" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1713" s="7">
+        <v>30</v>
+      </c>
+      <c r="C1713" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1714" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1714" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1714" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1715" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1715" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1715" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1716" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1716" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1716" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1717" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1717" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1717" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1718" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1718" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1718" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1719" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1719" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1719" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1720" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1720" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1720" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1721" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1721" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1721" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1722" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1722" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1722" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1723" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1723" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1723" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1724" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1724" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1724" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1725" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1725" s="7">
+        <v>21</v>
+      </c>
+      <c r="C1725" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1726" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1726" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1726" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1727" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1727" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1727" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1728" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1728" s="7">
+        <v>48</v>
+      </c>
+      <c r="C1728" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1729" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1729" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1729" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1730" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1730" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1730" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1731" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1731" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1731" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1732" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1732" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1732" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1733" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1733" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1733" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1734" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1734" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1734" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1735" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1735" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1735" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1736" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1736" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1736" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1737" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1737" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1737" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1738" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1738" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1738" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1739" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1739" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1739" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1740" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1740" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1740" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1741" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1741" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C1741" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1742" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1742" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1742" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1743" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1743" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1743" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1744" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1744" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1744" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1745" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1745" s="7">
+        <v>19</v>
+      </c>
+      <c r="C1745" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1746" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1746" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1746" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1747" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1747" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1747" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1748" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1748" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1748" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1749" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1749" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1749" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1750" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1750" s="7">
+        <v>46</v>
+      </c>
+      <c r="C1750" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1751" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1751" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1751" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1752" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1752" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1752" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1753" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1753" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1753" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1754" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1754" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1754" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1755" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1755" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1755" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1756" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1756" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1756" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1757" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1757" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1757" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1758" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1758" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1758" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1759" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1759" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1759" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1760" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1760" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1760" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1761" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1761" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C1761" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1762" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1762" s="7">
+        <v>22</v>
+      </c>
+      <c r="C1762" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1763" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1763" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1763" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1764" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1764" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1764" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1765" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1765" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1765" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1766" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1766" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1766" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1767" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1767" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C1767" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1768" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1768" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1768" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1769" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1769" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1769" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1770" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1770" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1770" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1771" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1771" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1771" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1772" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1772" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1772" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1773" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1773" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1773" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1774" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1774" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1774" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1775" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1775" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1775" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1776" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1776" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1776" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1777" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1777" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1777" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1778" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1778" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1778" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1779" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1779" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1779" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1780" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1780" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1780" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1781" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1781" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1781" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1782" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1782" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1782" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1783" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1783" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1783" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1784" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1784" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1784" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1785" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1785" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1785" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1786" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1786" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1786" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1787" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1787" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1787" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1788" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1788" s="7">
+        <v>29</v>
+      </c>
+      <c r="C1788" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1789" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1789" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1789" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1790" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1790" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1790" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1791" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1791" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1791" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1792" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1792" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1792" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1793" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1793" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C1793" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1794" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1794" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1794" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1795" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1795" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1795" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1796" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1796" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1796" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1797" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1797" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1797" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1798" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1798" s="7">
+        <v>26</v>
+      </c>
+      <c r="C1798" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1799" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1799" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C1799" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1800" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1800" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1800" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1801" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1801" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1801" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1802" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1802" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1802" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1803" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1803" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1803" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1804" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1804" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1804" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1805" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1805" s="7">
+        <v>28</v>
+      </c>
+      <c r="C1805" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1806" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1806" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C1806" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1807" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1807" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1807" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1808" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1808" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1808" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1809" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1809" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1809" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1810" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1810" s="7">
+        <v>220</v>
+      </c>
+      <c r="C1810" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1811" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1811" s="7">
+        <v>220</v>
+      </c>
+      <c r="C1811" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1812" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1812" s="7">
+        <v>190</v>
+      </c>
+      <c r="C1812" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1813" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1813" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1813" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1814" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1814" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1814" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1815" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1815" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1815" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1816" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1816" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1816" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1817" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1817" s="7">
+        <v>60</v>
+      </c>
+      <c r="C1817" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1818" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1818" s="7">
+        <v>170</v>
+      </c>
+      <c r="C1818" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1819" s="7">
+        <v>95</v>
+      </c>
+      <c r="C1819" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1820" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1820" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1820" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1821" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1821" s="7">
+        <v>44.5</v>
+      </c>
+      <c r="C1821" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1822" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1822" s="7">
+        <v>47</v>
+      </c>
+      <c r="C1822" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1823" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1823" s="7">
+        <v>46.5</v>
+      </c>
+      <c r="C1823" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1824" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1824" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1824" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1825" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1825" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1825" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1826" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1826" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1826" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1827" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1827" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1827" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1828" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1828" s="7">
+        <v>31</v>
+      </c>
+      <c r="C1828" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1829" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1829" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1829" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1830" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1830" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1830" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1831" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1831" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1831" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1832" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1832" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1832" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1833" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1833" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1833" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1834" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1834" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1834" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1835" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1835" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1835" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1836" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1836" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1836" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1837" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1837" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1837" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1838" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1838" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1838" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1839" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1839" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1839" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1840" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1840" s="7">
+        <v>22</v>
+      </c>
+      <c r="C1840" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1841" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1841" s="7">
+        <v>23</v>
+      </c>
+      <c r="C1841" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1842" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1842" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1842" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1843" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1843" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1843" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1844" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1844" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1844" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1845" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1845" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1845" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1846" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1846" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C1846" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1847" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1847" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1847" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1848" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1848" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1848" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1849" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1849" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1849" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1850" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1850" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C1850" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1851" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1851" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C1851" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1852" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1852" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1852" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1853" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1853" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1853" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1854" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1854" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1854" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1855" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1855" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1855" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1856" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1856" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1856" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1857" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1857" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1857" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1858" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1858" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1858" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1859" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1859" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1859" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1860" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1860" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1860" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1861" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1861" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1861" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1862" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1862" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1862" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1863" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1863" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C1863" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1864" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1864" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1864" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1865" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1865" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1865" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1866" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1866" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1866" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1867" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1867" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1867" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1868" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1868" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1868" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1869" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1869" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1869" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1870" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1870" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1870" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1871" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1871" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1871" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1872" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1872" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1872" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1873" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1873" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1873" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1874" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1874" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1874" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1875" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1875" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1875" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1876" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1876" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C1876" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1877" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1877" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1877" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1878" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1878" s="7">
+        <v>6</v>
+      </c>
+      <c r="C1878" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1879" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1879" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1879" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1880" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1880" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1880" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1881" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1881" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1881" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1882" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1882" s="7">
+        <v>65</v>
+      </c>
+      <c r="C1882" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1883" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1883" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1883" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1884" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1884" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1884" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1885" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1885" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1885" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1886" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1886" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1886" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1887" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1887" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1887" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1888" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1888" s="7">
+        <v>35</v>
+      </c>
+      <c r="C1888" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1889" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1889" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1889" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1890" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1890" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1890" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1891" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1891" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1891" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1892" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1892" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1892" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1893" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1893" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1893" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1894" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1894" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1894" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1895" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1895" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1895" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1896" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1896" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1896" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1897" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1897" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C1897" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1898" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1898" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1898" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1899" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1899" s="7">
+        <v>50</v>
+      </c>
+      <c r="C1899" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1900" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1900" s="7">
+        <v>60</v>
+      </c>
+      <c r="C1900" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1901" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1901" s="7">
+        <v>45</v>
+      </c>
+      <c r="C1901" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1902" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1902" s="7">
+        <v>18</v>
+      </c>
+      <c r="C1902" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1903" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1903" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1903" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1904" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1904" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1904" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1905" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1905" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1905" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1906" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1906" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1906" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1907" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1907" s="7">
+        <v>39</v>
+      </c>
+      <c r="C1907" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1908" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1908" s="7">
+        <v>24</v>
+      </c>
+      <c r="C1908" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1909" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1909" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C1909" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1910" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1910" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1910" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1911" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1911" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1911" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1912" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1912" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C1912" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1913" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1913" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C1913" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1914" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1914" s="7">
+        <v>25</v>
+      </c>
+      <c r="C1914" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1915" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1915" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1915" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1916" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1916" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1916" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1917" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1917" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1917" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1918" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1918" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1918" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1919" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1919" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1919" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1920" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1920" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1920" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1921" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1921" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1921" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1922" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1922" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1922" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1923" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1923" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1923" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1924" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1924" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1924" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1925" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1925" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1925" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1926" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1926" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C1926" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1927" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1927" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C1927" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1928" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1928" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1928" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1929" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1929" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C1929" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1930" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1930" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1930" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1931" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1931" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C1931" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1932" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1932" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1932" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1933" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1933" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1933" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1934" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1934" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1934" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1935" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1935" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1935" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1936" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1936" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1936" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1937" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1937" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1937" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1938" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1938" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1938" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1939" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1939" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1939" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1940" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1940" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1940" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1941" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1941" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1941" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1942" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1942" s="7">
+        <v>5</v>
+      </c>
+      <c r="C1942" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1943" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1943" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1943" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1944" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1944" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C1944" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1945" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1945" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1945" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1946" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1946" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1946" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1947" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1947" s="7">
+        <v>13</v>
+      </c>
+      <c r="C1947" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1948" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1948" s="7">
+        <v>9</v>
+      </c>
+      <c r="C1948" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1949" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1949" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1949" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1950" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1950" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C1950" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1951" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1951" s="7">
+        <v>24</v>
+      </c>
+      <c r="C1951" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1952" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1952" s="7">
+        <v>20</v>
+      </c>
+      <c r="C1952" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1953" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1953" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C1953" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1954" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1954" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1954" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1955" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1955" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1955" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1956" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1956" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1956" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1957" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1957" s="7">
+        <v>11</v>
+      </c>
+      <c r="C1957" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1958" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1958" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1958" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1959" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1959" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C1959" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1960" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1960" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1960" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1961" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1961" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C1961" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1962" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1962" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1962" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1963" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1963" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1963" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1964" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1964" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1964" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1965" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1965" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1965" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1966" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1966" s="7">
+        <v>8</v>
+      </c>
+      <c r="C1966" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1967" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1967" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1967" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1968" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1968" s="7">
+        <v>14</v>
+      </c>
+      <c r="C1968" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1969" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1969" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1969" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1970" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1970" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1970" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1971" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1971" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1971" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1972" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1972" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1972" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1973" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1973" s="7">
+        <v>23</v>
+      </c>
+      <c r="C1973" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1974" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1974" s="7">
+        <v>24</v>
+      </c>
+      <c r="C1974" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1975" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1975" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1975" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1976" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1976" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1976" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1977" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1977" s="7">
+        <v>22</v>
+      </c>
+      <c r="C1977" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1978" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1978" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C1978" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1979" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1979" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C1979" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1980" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1980" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C1980" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1981" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1981" s="7">
+        <v>16</v>
+      </c>
+      <c r="C1981" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1982" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1982" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C1982" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1983" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1983" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C1983" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1984" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1984" s="7">
+        <v>65</v>
+      </c>
+      <c r="C1984" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1985" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1985" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1985" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1986" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1986" s="7">
+        <v>12</v>
+      </c>
+      <c r="C1986" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1987" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1987" s="7">
+        <v>37.5</v>
+      </c>
+      <c r="C1987" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1988" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1988" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C1988" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1989" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1989" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C1989" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1990" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1990" s="7">
+        <v>31</v>
+      </c>
+      <c r="C1990" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1991" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1991" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C1991" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1992" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1992" s="7">
+        <v>27</v>
+      </c>
+      <c r="C1992" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1993" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1993" s="7">
+        <v>17</v>
+      </c>
+      <c r="C1993" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1994" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1994" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C1994" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1995" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1995" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C1995" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1996" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1996" s="7">
+        <v>15</v>
+      </c>
+      <c r="C1996" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1997" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1997" s="7">
+        <v>10</v>
+      </c>
+      <c r="C1997" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1998" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1998" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1998" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1999" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B1999" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C1999" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2000" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2000" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2000" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2001" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2001" s="7">
+        <v>2</v>
+      </c>
+      <c r="C2001" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2002" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2002" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C2002" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2003" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2003" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2003" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2004" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2004" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C2004" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2005" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2005" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2005" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2006" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2006" s="7">
+        <v>75</v>
+      </c>
+      <c r="C2006" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2007" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2007" s="7">
+        <v>55</v>
+      </c>
+      <c r="C2007" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2008" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2008" s="7">
+        <v>35</v>
+      </c>
+      <c r="C2008" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2009" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2009" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2009" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2010" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2010" s="7">
+        <v>29</v>
+      </c>
+      <c r="C2010" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2011" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2011" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C2011" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2012" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2012" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2012" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2013" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2013" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2013" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2014" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2014" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2014" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2015" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2015" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C2015" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2016" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2016" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2016" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2017" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2017" s="7">
+        <v>4</v>
+      </c>
+      <c r="C2017" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2018" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2018" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2018" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2019" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2019" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2019" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2020" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2020" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2020" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2021" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2021" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2021" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2022" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2022" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C2022" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2023" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2023" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2023" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2024" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2024" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C2024" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2025" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2025" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C2025" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2026" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2026" s="7">
+        <v>27</v>
+      </c>
+      <c r="C2026" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2027" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2027" s="7">
+        <v>18</v>
+      </c>
+      <c r="C2027" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2028" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2028" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C2028" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2029" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2029" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2029" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2030" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2030" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C2030" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2031" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2031" s="7">
+        <v>110</v>
+      </c>
+      <c r="C2031" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2032" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2032" s="7">
+        <v>115</v>
+      </c>
+      <c r="C2032" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2033" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2033" s="7">
+        <v>130</v>
+      </c>
+      <c r="C2033" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2034" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2034" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2034" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2035" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2035" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C2035" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2036" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2036" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2036" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2037" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2037" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2037" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2038" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2038" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2038" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2039" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2039" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C2039" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2040" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2040" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C2040" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2041" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2041" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2041" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2042" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2042" s="7">
+        <v>5</v>
+      </c>
+      <c r="C2042" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2043" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2043" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C2043" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2044" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2044" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2044" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2045" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2045" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2045" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2046" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2046" s="7">
+        <v>75</v>
+      </c>
+      <c r="C2046" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2047" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2047" s="7">
+        <v>85</v>
+      </c>
+      <c r="C2047" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2048" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2048" s="7">
+        <v>65</v>
+      </c>
+      <c r="C2048" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2049" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2049" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C2049" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2050" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2050" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C2050" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2051" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2051" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2051" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2052" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2052" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C2052" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2053" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2053" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2053" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2054" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2054" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2054" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2055" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2055" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C2055" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2056" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2056" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2056" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2057" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2057" s="7">
+        <v>14</v>
+      </c>
+      <c r="C2057" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2058" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2058" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2058" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2059" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2059" s="7">
+        <v>20</v>
+      </c>
+      <c r="C2059" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2060" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2060" s="7">
+        <v>35</v>
+      </c>
+      <c r="C2060" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2061" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2061" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C2061" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2062" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2062" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C2062" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2063" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2063" s="7">
+        <v>11</v>
+      </c>
+      <c r="C2063" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2064" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2064" s="7">
+        <v>13</v>
+      </c>
+      <c r="C2064" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2065" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2065" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2065" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2066" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2066" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2066" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2067" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2067" s="7">
+        <v>40</v>
+      </c>
+      <c r="C2067" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2068" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2068" s="7">
+        <v>45</v>
+      </c>
+      <c r="C2068" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2069" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2069" s="7">
+        <v>55</v>
+      </c>
+      <c r="C2069" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2070" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2070" s="7">
+        <v>5</v>
+      </c>
+      <c r="C2070" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2071" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2071" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C2071" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2072" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2072" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2072" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2073" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2073" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2073" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2074" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2074" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C2074" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2075" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2075" s="7">
+        <v>15</v>
+      </c>
+      <c r="C2075" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2076" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2076" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2076" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2077" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2077" s="7">
+        <v>14</v>
+      </c>
+      <c r="C2077" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2078" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2078" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2078" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2079" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2079" s="7">
+        <v>40</v>
+      </c>
+      <c r="C2079" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2080" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2080" s="7">
+        <v>35</v>
+      </c>
+      <c r="C2080" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2081" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2081" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2081" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2082" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2082" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2082" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2083" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2083" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2083" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2084" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2084" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C2084" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2085" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2085" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2085" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2086" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2086" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C2086" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2087" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2087" s="7">
+        <v>26</v>
+      </c>
+      <c r="C2087" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2088" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2088" s="7">
+        <v>15</v>
+      </c>
+      <c r="C2088" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2089" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2089" s="7">
+        <v>36.5</v>
+      </c>
+      <c r="C2089" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2090" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2090" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2090" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2091" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2091" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C2091" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2092" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2092" s="7">
+        <v>5</v>
+      </c>
+      <c r="C2092" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2093" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2093" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C2093" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2094" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2094" s="7">
+        <v>13</v>
+      </c>
+      <c r="C2094" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2095" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2095" s="7">
+        <v>15</v>
+      </c>
+      <c r="C2095" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2096" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2096" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C2096" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2097" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2097" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C2097" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2098" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2098" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2098" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2099" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2099" s="7">
+        <v>19</v>
+      </c>
+      <c r="C2099" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2100" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2100" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2100" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2101" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2101" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2101" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2102" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2102" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2102" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2103" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2103" s="7">
+        <v>24</v>
+      </c>
+      <c r="C2103" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2104" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2104" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C2104" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2105" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2105" s="7">
+        <v>50</v>
+      </c>
+      <c r="C2105" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2106" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2106" s="7">
+        <v>35</v>
+      </c>
+      <c r="C2106" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2107" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2107" s="7">
+        <v>65</v>
+      </c>
+      <c r="C2107" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2108" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2108" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2108" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2109" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2109" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C2109" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2110" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2110" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2110" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2111" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2111" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2111" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2112" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2112" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2112" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2113" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2113" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2113" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2114" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2114" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2114" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2115" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2115" s="7">
+        <v>13</v>
+      </c>
+      <c r="C2115" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2116" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2116" s="7">
+        <v>24</v>
+      </c>
+      <c r="C2116" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2117" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2117" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2117" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2118" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2118" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2118" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2119" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2119" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2119" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2120" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2120" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2120" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2121" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2121" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2121" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2122" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2122" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2122" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2123" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2123" s="7">
+        <v>2</v>
+      </c>
+      <c r="C2123" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2124" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2124" s="7">
+        <v>37.5</v>
+      </c>
+      <c r="C2124" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2125" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2125" s="7">
+        <v>19</v>
+      </c>
+      <c r="C2125" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2126" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2126" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C2126" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2127" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2127" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C2127" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2128" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2128" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2128" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2129" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2129" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C2129" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2130" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2130" s="7">
+        <v>31</v>
+      </c>
+      <c r="C2130" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2131" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2131" s="7">
+        <v>38.5</v>
+      </c>
+      <c r="C2131" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2132" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2132" s="7">
+        <v>19</v>
+      </c>
+      <c r="C2132" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2133" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2133" s="7">
+        <v>14</v>
+      </c>
+      <c r="C2133" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2134" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2134" s="7">
+        <v>5</v>
+      </c>
+      <c r="C2134" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2135" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2135" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C2135" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2136" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2136" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C2136" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2137" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2137" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C2137" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2138" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2138" s="7">
+        <v>26</v>
+      </c>
+      <c r="C2138" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2139" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2139" s="7">
+        <v>60</v>
+      </c>
+      <c r="C2139" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2140" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2140" s="7">
+        <v>70</v>
+      </c>
+      <c r="C2140" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2141" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2141" s="7">
+        <v>50</v>
+      </c>
+      <c r="C2141" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2142" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2142" s="7">
+        <v>28</v>
+      </c>
+      <c r="C2142" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2143" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2143" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2143" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2144" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2144" s="7">
+        <v>11</v>
+      </c>
+      <c r="C2144" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2145" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2145" s="7">
+        <v>14</v>
+      </c>
+      <c r="C2145" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2146" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2146" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2146" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2147" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2147" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2147" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2148" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2148" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2148" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2149" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2149" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2149" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2150" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2150" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C2150" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2151" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2151" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2151" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2152" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2152" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2152" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2153" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2153" s="7">
+        <v>40.5</v>
+      </c>
+      <c r="C2153" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2154" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2154" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="C2154" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2155" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2155" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2155" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2156" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2156" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2156" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2157" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2157" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2157" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2158" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2158" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2158" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2159" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2159" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C2159" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2160" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2160" s="7">
+        <v>22</v>
+      </c>
+      <c r="C2160" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2161" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2161" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C2161" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2162" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2162" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2162" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2163" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2163" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C2163" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2164" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2164" s="7">
+        <v>19</v>
+      </c>
+      <c r="C2164" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2165" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2165" s="7">
+        <v>4</v>
+      </c>
+      <c r="C2165" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2166" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2166" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2166" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2167" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2167" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2167" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2168" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2168" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2168" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2169" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2169" s="7">
+        <v>11</v>
+      </c>
+      <c r="C2169" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2170" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2170" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2170" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2171" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2171" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2171" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2172" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2172" s="7">
+        <v>13</v>
+      </c>
+      <c r="C2172" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2173" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2173" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2173" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2174" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2174" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2174" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2175" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2175" s="7">
+        <v>65</v>
+      </c>
+      <c r="C2175" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2176" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2176" s="7">
+        <v>55</v>
+      </c>
+      <c r="C2176" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2177" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2177" s="7">
+        <v>55</v>
+      </c>
+      <c r="C2177" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2178" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2178" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2178" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2179" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2179" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2179" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2180" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2180" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2180" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2181" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2181" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C2181" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2182" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2182" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C2182" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2183" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2183" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2183" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2184" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2184" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2184" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2185" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2185" s="7">
+        <v>4</v>
+      </c>
+      <c r="C2185" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2186" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2186" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C2186" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2187" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2187" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C2187" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2188" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2188" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C2188" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2189" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2189" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2189" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2190" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2190" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2190" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2191" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2191" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C2191" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2192" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2192" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2192" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2193" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2193" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2193" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2194" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2194" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C2194" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2195" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2195" s="7">
+        <v>18</v>
+      </c>
+      <c r="C2195" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2196" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2196" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2196" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2197" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2197" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C2197" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2198" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2198" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2198" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2199" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2199" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C2199" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2200" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2200" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2200" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2201" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2201" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2201" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2202" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2202" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C2202" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2203" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2203" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2203" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2204" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2204" s="7">
+        <v>15</v>
+      </c>
+      <c r="C2204" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2205" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2205" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2205" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2206" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2206" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C2206" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2207" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2207" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2207" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2208" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2208" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2208" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2209" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2209" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C2209" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2210" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2210" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2210" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2211" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2211" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C2211" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2212" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2212" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2212" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2213" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2213" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2213" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2214" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2214" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2214" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2215" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2215" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2215" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2216" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2216" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2216" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2217" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2217" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C2217" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2218" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2218" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2218" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2219" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2219" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C2219" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2220" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2220" s="7">
+        <v>13</v>
+      </c>
+      <c r="C2220" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2221" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2221" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2221" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2222" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2222" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2222" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2223" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2223" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C2223" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2224" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2224" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C2224" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2225" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2225" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2225" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2226" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2226" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2226" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2227" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2227" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2227" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2228" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2228" s="7">
+        <v>10</v>
+      </c>
+      <c r="C2228" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2229" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2229" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2229" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2230" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2230" s="7">
+        <v>24</v>
+      </c>
+      <c r="C2230" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2231" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2231" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C2231" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2232" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2232" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C2232" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2233" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2233" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2233" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2234" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2234" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2234" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2235" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2235" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2235" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2236" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2236" s="7">
+        <v>34</v>
+      </c>
+      <c r="C2236" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2237" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2237" s="7">
+        <v>15</v>
+      </c>
+      <c r="C2237" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2238" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2238" s="7">
+        <v>135</v>
+      </c>
+      <c r="C2238" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2239" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2239" s="7">
+        <v>130</v>
+      </c>
+      <c r="C2239" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2240" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2240" s="7">
+        <v>105</v>
+      </c>
+      <c r="C2240" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2241" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2241" s="7">
+        <v>23</v>
+      </c>
+      <c r="C2241" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2242" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2242" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C2242" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2243" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2243" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2243" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2244" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2244" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2244" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2245" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2245" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2245" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2246" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2246" s="7">
+        <v>20</v>
+      </c>
+      <c r="C2246" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2247" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2247" s="7">
+        <v>22</v>
+      </c>
+      <c r="C2247" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2248" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2248" s="7">
+        <v>11</v>
+      </c>
+      <c r="C2248" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2249" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2249" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C2249" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2250" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2250" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C2250" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2251" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2251" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C2251" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2252" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2252" s="7">
+        <v>18</v>
+      </c>
+      <c r="C2252" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2253" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2253" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2253" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2254" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2254" s="7">
+        <v>22</v>
+      </c>
+      <c r="C2254" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2255" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2255" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C2255" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2256" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2256" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C2256" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2257" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2257" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2257" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2258" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2258" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2258" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2259" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2259" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2259" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2260" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2260" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C2260" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2261" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2261" s="7">
+        <v>23</v>
+      </c>
+      <c r="C2261" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2262" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2262" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C2262" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2263" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2263" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C2263" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2264" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2264" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C2264" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2265" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2265" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2265" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2266" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2266" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2266" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2267" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2267" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2267" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2268" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2268" s="7">
+        <v>90</v>
+      </c>
+      <c r="C2268" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2269" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2269" s="7">
+        <v>10</v>
+      </c>
+      <c r="C2269" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2270" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2270" s="7">
+        <v>24</v>
+      </c>
+      <c r="C2270" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2271" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2271" s="7">
+        <v>29</v>
+      </c>
+      <c r="C2271" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2272" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2272" s="7">
+        <v>30</v>
+      </c>
+      <c r="C2272" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2273" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2273" s="7">
+        <v>9</v>
+      </c>
+      <c r="C2273" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2274" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2274" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2274" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2275" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2275" s="7">
+        <v>4</v>
+      </c>
+      <c r="C2275" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2276" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2276" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C2276" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2277" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2277" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2277" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2278" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2278" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2278" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2279" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2279" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2279" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2280" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2280" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C2280" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2281" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2281" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2281" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2282" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2282" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C2282" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2283" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2283" s="7">
+        <v>14</v>
+      </c>
+      <c r="C2283" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2284" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2284" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C2284" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2285" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2285" s="7">
+        <v>14</v>
+      </c>
+      <c r="C2285" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2286" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2286" s="7">
+        <v>5</v>
+      </c>
+      <c r="C2286" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2287" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2287" s="7">
+        <v>10</v>
+      </c>
+      <c r="C2287" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2288" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2288" s="7">
+        <v>13</v>
+      </c>
+      <c r="C2288" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2289" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2289" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C2289" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2290" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2290" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2290" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2291" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2291" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C2291" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2292" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2292" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C2292" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2293" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2293" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C2293" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2294" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2294" s="7">
+        <v>29</v>
+      </c>
+      <c r="C2294" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2295" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2295" s="7">
+        <v>23</v>
+      </c>
+      <c r="C2295" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2296" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2296" s="7">
+        <v>25</v>
+      </c>
+      <c r="C2296" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2297" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2297" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C2297" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2298" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2298" s="7">
+        <v>4</v>
+      </c>
+      <c r="C2298" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2299" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2299" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C2299" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2300" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2300" s="7">
+        <v>8</v>
+      </c>
+      <c r="C2300" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2301" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2301" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2301" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2302" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2302" s="7">
+        <v>6</v>
+      </c>
+      <c r="C2302" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2303" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2303" s="7">
+        <v>122</v>
+      </c>
+      <c r="C2303" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2304" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2304" s="7">
+        <v>80</v>
+      </c>
+      <c r="C2304" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2305" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2305" s="7">
+        <v>150</v>
+      </c>
+      <c r="C2305" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2306" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2306" s="7">
+        <v>150</v>
+      </c>
+      <c r="C2306" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2307" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2307" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C2307" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C1524">
+  <conditionalFormatting sqref="C2:C2307">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
